--- a/气劲/附魔气劲.xlsx
+++ b/气劲/附魔气劲.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -4788,6 +4788,318 @@
     <t>130级橙武_傲血战意_龙牙附致残</t>
   </si>
   <si>
+    <t>破招降低·无双提高</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·无双提高",key="创意食品",},</t>
+  </si>
+  <si>
+    <t>破招降低·内攻提高</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·内攻提高",key="创意食品",},</t>
+  </si>
+  <si>
+    <t>破招降低·外攻提高</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·外攻提高",key="创意食品",},</t>
+  </si>
+  <si>
+    <t>破招降低·破防提高</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·破防提高",key="创意食品",},</t>
+  </si>
+  <si>
+    <t>破招降低·会心提高</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·会心提高",key="创意食品",},</t>
+  </si>
+  <si>
+    <t>无双降低·破招提高</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·破招提高",key="创意食品",},</t>
+  </si>
+  <si>
+    <t>无双降低·内攻提高</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·内攻提高",key="创意食品",},</t>
+  </si>
+  <si>
+    <t>无双降低·外攻提高</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·外攻提高",key="创意食品",},</t>
+  </si>
+  <si>
+    <t>无双降低·破防提高</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·破防提高",key="创意食品",},</t>
+  </si>
+  <si>
+    <t>无双降低·会心提高</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·会心提高",key="创意食品",},</t>
+  </si>
+  <si>
+    <t>气血降低·无双提高</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·无双提高",key="创意食品",},</t>
+  </si>
+  <si>
+    <t>气血降低·内攻提高</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·内攻提高",key="创意食品",},</t>
+  </si>
+  <si>
+    <t>气血降低·外攻提高</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·外攻提高",key="创意食品",},</t>
+  </si>
+  <si>
+    <t>气血降低·破防提高</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·破防提高",key="创意食品",},</t>
+  </si>
+  <si>
+    <t>气血降低·会心提高</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·会心提高",key="创意食品",},</t>
+  </si>
+  <si>
+    <t>鞋会心</t>
+  </si>
+  <si>
+    <t>PVP附魔2鞋子战阶_雷特效_太极秘录</t>
+  </si>
+  <si>
+    <t>鞋移速</t>
+  </si>
+  <si>
+    <t>PVP附魔1鞋子_移速</t>
+  </si>
+  <si>
+    <t>29,238,255,</t>
+  </si>
+  <si>
+    <t>鞋伤疗</t>
+  </si>
+  <si>
+    <t>PVP附魔1鞋子战阶_水特效_太极秘录</t>
+  </si>
+  <si>
+    <t>衣护盾</t>
+  </si>
+  <si>
+    <t>PVP附魔2上衣_护盾_太极秘录</t>
+  </si>
+  <si>
+    <t>衣恢复</t>
+  </si>
+  <si>
+    <t>PVP附魔1上衣战阶_持续回复效果_太极秘录</t>
+  </si>
+  <si>
+    <t>头特效</t>
+  </si>
+  <si>
+    <t>PVP附魔1帽子_密玉BUFF</t>
+  </si>
+  <si>
+    <t>化转御</t>
+  </si>
+  <si>
+    <t>PVP附魔2腰带战阶_化劲转御劲_太极秘录</t>
+  </si>
+  <si>
+    <t>腰御劲</t>
+  </si>
+  <si>
+    <t>PVP附魔1腰带战阶_被击加御劲_太极秘录</t>
+  </si>
+  <si>
+    <t>手会心</t>
+  </si>
+  <si>
+    <t>PVP附魔2护手战阶_全会心添加_太极秘录</t>
+  </si>
+  <si>
+    <t>手特效</t>
+  </si>
+  <si>
+    <t>PVP附魔1护手拍卖_效果添加</t>
+  </si>
+  <si>
+    <t>腰护盾</t>
+  </si>
+  <si>
+    <t>PVP腰带护盾</t>
+  </si>
+  <si>
+    <t>PVP鞋子受击加移速20%</t>
+  </si>
+  <si>
+    <t>裤治疗</t>
+  </si>
+  <si>
+    <t>治疗PVP裤子加治疗</t>
+  </si>
+  <si>
+    <t>裤攻击</t>
+  </si>
+  <si>
+    <t>输出PVP裤子加攻击</t>
+  </si>
+  <si>
+    <t>风腰坠</t>
+  </si>
+  <si>
+    <t>PVP风·斩流</t>
+  </si>
+  <si>
+    <t>["SKILL#10028"]=true,["SKILL#10080"]=true,["SKILL#10176"]=true,["SKILL#10448"]=true,["SKILL#10626"]=true,</t>
+  </si>
+  <si>
+    <t>沐风-基础治疗量提高</t>
+  </si>
+  <si>
+    <t>水武器</t>
+  </si>
+  <si>
+    <t>水·鋭刃-水特效武器</t>
+  </si>
+  <si>
+    <t>雷武器</t>
+  </si>
+  <si>
+    <t>雷·鋭刃-雷特效武器</t>
+  </si>
+  <si>
+    <t>风·鋭刃-风特效腰坠</t>
+  </si>
+  <si>
+    <t>秘境的数据</t>
+  </si>
+  <si>
+    <t>肘子菜盘</t>
+  </si>
+  <si>
+    <t>{nClass=2,nIcon=546,nFrame=5,nTime=2,szName="肘子菜盘·消失",nRefresh=60,key="帮会外食",},</t>
+  </si>
+  <si>
+    <t>南瓜盅菜盘</t>
+  </si>
+  <si>
+    <t>{nClass=2,nIcon=1546,nFrame=5,nTime=3,szName="南瓜盅菜盘·消失",nRefresh=60,key="帮会外食",},</t>
+  </si>
+  <si>
+    <t>烧鸡外食</t>
+  </si>
+  <si>
+    <t>{nClass=2,nIcon=171,nFrame=5,nTime=2,szName="烧鸡外食·消失",nRefresh=60,key="帮会外食",},</t>
+  </si>
+  <si>
+    <t>蒸鱼菜盘</t>
+  </si>
+  <si>
+    <t>{nClass=2,nIcon=552,nFrame=5,nTime=3,szName="蒸鱼菜盘·消失",nRefresh=60,key="帮会外食",},</t>
+  </si>
+  <si>
+    <t>鸡肉菜盘</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=264,nFrame=5,nTime=2,szName="已食用·鸡肉菜盘5%",nRefresh=5,key="绣球花",},</t>
+  </si>
+  <si>
+    <t>{nClass=2,nIcon=264,nFrame=5,nTime=2,szName="鸡肉菜盘·已消失",key="绣球花",},</t>
+  </si>
+  <si>
+    <t>龙葵</t>
+  </si>
+  <si>
+    <t>葵</t>
+  </si>
+  <si>
+    <t>#00FF00FF</t>
+  </si>
+  <si>
+    <t>#00FF00</t>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=15413,nFrame=6,nTime=7,szName="龙葵自苦·[{$sender}]",key="减伤监控",},</t>
+  </si>
+  <si>
+    <t>述怀</t>
+  </si>
+  <si>
+    <t>述</t>
+  </si>
+  <si>
+    <t>#00EE00FF</t>
+  </si>
+  <si>
+    <t>翔舞</t>
+  </si>
+  <si>
+    <t>翔</t>
+  </si>
+  <si>
+    <t>上元点鬟</t>
+  </si>
+  <si>
+    <t>元</t>
+  </si>
+  <si>
+    <t>赤芍寒香</t>
+  </si>
+  <si>
+    <t>芍</t>
+  </si>
+  <si>
+    <t>梅花三弄</t>
+  </si>
+  <si>
+    <t>31,255,238,</t>
+  </si>
+  <si>
+    <t>梅</t>
+  </si>
+  <si>
+    <t>#1FFFEEFF</t>
+  </si>
+  <si>
+    <t>宫</t>
+  </si>
+  <si>
+    <t>商</t>
+  </si>
+  <si>
+    <t>角</t>
+  </si>
+  <si>
+    <t>握针</t>
+  </si>
+  <si>
+    <t>握</t>
+  </si>
+  <si>
+    <t>野外地图的数据</t>
+  </si>
+  <si>
+    <t>return {DEBUFF={</t>
+  </si>
+  <si>
     <t>缘会·今夕何夕</t>
   </si>
   <si>
@@ -4813,318 +5125,6 @@
   </si>
   <si>
     <t>{nClass=2,nIcon=21600,nFrame=2,nTime=60,szName="香膏·宠物奇遇·已消失",key="缘会·山有扶苏",},</t>
-  </si>
-  <si>
-    <t>破招降低·无双提高</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·无双提高",key="创意食品",},</t>
-  </si>
-  <si>
-    <t>破招降低·内攻提高</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·内攻提高",key="创意食品",},</t>
-  </si>
-  <si>
-    <t>破招降低·外攻提高</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·外攻提高",key="创意食品",},</t>
-  </si>
-  <si>
-    <t>破招降低·破防提高</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·破防提高",key="创意食品",},</t>
-  </si>
-  <si>
-    <t>破招降低·会心提高</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·会心提高",key="创意食品",},</t>
-  </si>
-  <si>
-    <t>无双降低·破招提高</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·破招提高",key="创意食品",},</t>
-  </si>
-  <si>
-    <t>无双降低·内攻提高</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·内攻提高",key="创意食品",},</t>
-  </si>
-  <si>
-    <t>无双降低·外攻提高</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·外攻提高",key="创意食品",},</t>
-  </si>
-  <si>
-    <t>无双降低·破防提高</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·破防提高",key="创意食品",},</t>
-  </si>
-  <si>
-    <t>无双降低·会心提高</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·会心提高",key="创意食品",},</t>
-  </si>
-  <si>
-    <t>气血降低·无双提高</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·无双提高",key="创意食品",},</t>
-  </si>
-  <si>
-    <t>气血降低·内攻提高</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·内攻提高",key="创意食品",},</t>
-  </si>
-  <si>
-    <t>气血降低·外攻提高</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·外攻提高",key="创意食品",},</t>
-  </si>
-  <si>
-    <t>气血降低·破防提高</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·破防提高",key="创意食品",},</t>
-  </si>
-  <si>
-    <t>气血降低·会心提高</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·会心提高",key="创意食品",},</t>
-  </si>
-  <si>
-    <t>鞋会心</t>
-  </si>
-  <si>
-    <t>PVP附魔2鞋子战阶_雷特效_太极秘录</t>
-  </si>
-  <si>
-    <t>鞋移速</t>
-  </si>
-  <si>
-    <t>PVP附魔1鞋子_移速</t>
-  </si>
-  <si>
-    <t>29,238,255,</t>
-  </si>
-  <si>
-    <t>鞋伤疗</t>
-  </si>
-  <si>
-    <t>PVP附魔1鞋子战阶_水特效_太极秘录</t>
-  </si>
-  <si>
-    <t>衣护盾</t>
-  </si>
-  <si>
-    <t>PVP附魔2上衣_护盾_太极秘录</t>
-  </si>
-  <si>
-    <t>衣恢复</t>
-  </si>
-  <si>
-    <t>PVP附魔1上衣战阶_持续回复效果_太极秘录</t>
-  </si>
-  <si>
-    <t>头特效</t>
-  </si>
-  <si>
-    <t>PVP附魔1帽子_密玉BUFF</t>
-  </si>
-  <si>
-    <t>化转御</t>
-  </si>
-  <si>
-    <t>PVP附魔2腰带战阶_化劲转御劲_太极秘录</t>
-  </si>
-  <si>
-    <t>腰御劲</t>
-  </si>
-  <si>
-    <t>PVP附魔1腰带战阶_被击加御劲_太极秘录</t>
-  </si>
-  <si>
-    <t>手会心</t>
-  </si>
-  <si>
-    <t>PVP附魔2护手战阶_全会心添加_太极秘录</t>
-  </si>
-  <si>
-    <t>手特效</t>
-  </si>
-  <si>
-    <t>PVP附魔1护手拍卖_效果添加</t>
-  </si>
-  <si>
-    <t>腰护盾</t>
-  </si>
-  <si>
-    <t>PVP腰带护盾</t>
-  </si>
-  <si>
-    <t>PVP鞋子受击加移速20%</t>
-  </si>
-  <si>
-    <t>裤治疗</t>
-  </si>
-  <si>
-    <t>治疗PVP裤子加治疗</t>
-  </si>
-  <si>
-    <t>裤攻击</t>
-  </si>
-  <si>
-    <t>输出PVP裤子加攻击</t>
-  </si>
-  <si>
-    <t>风腰坠</t>
-  </si>
-  <si>
-    <t>PVP风·斩流</t>
-  </si>
-  <si>
-    <t>["SKILL#10028"]=true,["SKILL#10080"]=true,["SKILL#10176"]=true,["SKILL#10448"]=true,["SKILL#10626"]=true,</t>
-  </si>
-  <si>
-    <t>沐风-基础治疗量提高</t>
-  </si>
-  <si>
-    <t>水武器</t>
-  </si>
-  <si>
-    <t>水·鋭刃-水特效武器</t>
-  </si>
-  <si>
-    <t>雷武器</t>
-  </si>
-  <si>
-    <t>雷·鋭刃-雷特效武器</t>
-  </si>
-  <si>
-    <t>风·鋭刃-风特效腰坠</t>
-  </si>
-  <si>
-    <t>秘境的数据</t>
-  </si>
-  <si>
-    <t>肘子菜盘</t>
-  </si>
-  <si>
-    <t>{nClass=2,nIcon=546,nFrame=5,nTime=2,szName="肘子菜盘·消失",nRefresh=60,key="帮会外食",},</t>
-  </si>
-  <si>
-    <t>南瓜盅菜盘</t>
-  </si>
-  <si>
-    <t>{nClass=2,nIcon=1546,nFrame=5,nTime=3,szName="南瓜盅菜盘·消失",nRefresh=60,key="帮会外食",},</t>
-  </si>
-  <si>
-    <t>烧鸡外食</t>
-  </si>
-  <si>
-    <t>{nClass=2,nIcon=171,nFrame=5,nTime=2,szName="烧鸡外食·消失",nRefresh=60,key="帮会外食",},</t>
-  </si>
-  <si>
-    <t>蒸鱼菜盘</t>
-  </si>
-  <si>
-    <t>{nClass=2,nIcon=552,nFrame=5,nTime=3,szName="蒸鱼菜盘·消失",nRefresh=60,key="帮会外食",},</t>
-  </si>
-  <si>
-    <t>鸡肉菜盘</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=264,nFrame=5,nTime=2,szName="已食用·鸡肉菜盘5%",nRefresh=5,key="绣球花",},</t>
-  </si>
-  <si>
-    <t>{nClass=2,nIcon=264,nFrame=5,nTime=2,szName="鸡肉菜盘·已消失",key="绣球花",},</t>
-  </si>
-  <si>
-    <t>龙葵</t>
-  </si>
-  <si>
-    <t>葵</t>
-  </si>
-  <si>
-    <t>#00FF00FF</t>
-  </si>
-  <si>
-    <t>#00FF00</t>
-  </si>
-  <si>
-    <t>{nClass=1,nIcon=15413,nFrame=6,nTime=7,szName="龙葵自苦·[{$sender}]",key="减伤监控",},</t>
-  </si>
-  <si>
-    <t>述怀</t>
-  </si>
-  <si>
-    <t>述</t>
-  </si>
-  <si>
-    <t>#00EE00FF</t>
-  </si>
-  <si>
-    <t>翔舞</t>
-  </si>
-  <si>
-    <t>翔</t>
-  </si>
-  <si>
-    <t>上元点鬟</t>
-  </si>
-  <si>
-    <t>元</t>
-  </si>
-  <si>
-    <t>赤芍寒香</t>
-  </si>
-  <si>
-    <t>芍</t>
-  </si>
-  <si>
-    <t>梅花三弄</t>
-  </si>
-  <si>
-    <t>31,255,238,</t>
-  </si>
-  <si>
-    <t>梅</t>
-  </si>
-  <si>
-    <t>#1FFFEEFF</t>
-  </si>
-  <si>
-    <t>宫</t>
-  </si>
-  <si>
-    <t>商</t>
-  </si>
-  <si>
-    <t>角</t>
-  </si>
-  <si>
-    <t>握针</t>
-  </si>
-  <si>
-    <t>握</t>
-  </si>
-  <si>
-    <t>野外地图的数据</t>
-  </si>
-  <si>
-    <t>return {DEBUFF={</t>
   </si>
   <si>
     <t>头计数</t>
@@ -5236,13 +5236,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5807,28 +5801,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5837,49 +5834,46 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5891,7 +5885,7 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5903,7 +5897,7 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5915,7 +5909,7 @@
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5927,7 +5921,7 @@
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5939,7 +5933,7 @@
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5956,7 +5950,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5965,13 +5959,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -6004,19 +5998,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="22" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="22" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="6" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -6025,7 +6019,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6034,19 +6028,19 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="23" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="23" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="23" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="23" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6061,7 +6055,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -6449,7 +6443,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1785581301000,</v>
+        <v>nTimeStamp = 1785582480000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -16361,7 +16355,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AS99"/>
+  <dimension ref="A1:AS96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="8" max="8" width="9.75" customWidth="1"/>
@@ -17505,7 +17499,7 @@
         <v>{dwID=1913,nLevel=1,nIcon=23408,szName="橙武",nScrutinyType=1,tKungFu={["SKILL#10021"]=true,},szNote="130橙武_花间游_玉石附钟林毓秀",col={255,150,0,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
-    <row r="33" spans="3:45">
+    <row r="33" spans="3:44">
       <c r="C33">
         <v>1912</v>
       </c>
@@ -17538,7 +17532,7 @@
         <v>{dwID=1912,nLevel=1,nIcon=23406,szName="橙武",nScrutinyType=1,tKungFu={["SKILL#10062"]=true,},szNote="130橙武_铁牢律_威胁提高",col={255,150,0,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
-    <row r="34" spans="3:45">
+    <row r="34" spans="3:44">
       <c r="C34">
         <v>1911</v>
       </c>
@@ -17571,93 +17565,93 @@
         <v>{dwID=1911,nLevel=1,nIcon=23407,szName="橙武",nScrutinyType=1,tKungFu={["SKILL#10026"]=true,},szNote="130级橙武_傲血战意_龙牙附致残",col={255,150,0,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" spans="3:45">
-      <c r="C35" s="1">
-        <v>27689</v>
-      </c>
-      <c r="D35" s="1">
-        <v>1</v>
-      </c>
-      <c r="I35" s="1">
-        <v>1</v>
-      </c>
-      <c r="K35" s="1" t="s">
+    <row r="35" spans="3:44">
+      <c r="C35">
+        <v>17365</v>
+      </c>
+      <c r="D35">
+        <v>46</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="K35" t="s">
         <v>1581</v>
       </c>
-      <c r="L35" s="1" t="s">
-        <v>613</v>
+      <c r="L35" t="s">
+        <v>622</v>
       </c>
       <c r="AQ35" t="str">
         <f t="shared" ref="AQ35:AQ66" si="1">IF(B35&lt;&gt;"",IF(IFERROR(VALUE(C34),0)&lt;=0,"["&amp;B35&amp;"]={","},["&amp;B35&amp;"]={"),IF(C35&gt;0,"{dwID="&amp;C35&amp;","&amp;"nLevel="&amp;D35&amp;","&amp;IF(E35&gt;0,"nCount="&amp;E35&amp;",","")&amp;IF(F35&gt;0,"nIcon="&amp;F35&amp;",","")&amp;IF(G35&lt;&gt;"","szName="""&amp;G35&amp;""",","")&amp;IF(H35&gt;0,"bCheckLevel=true,","")&amp;IF(I35&gt;0,"nScrutinyType="&amp;I35&amp;",","")&amp;IF(J35&lt;&gt;"","tKungFu={"&amp;J35&amp;"},","")&amp;IF(K35&lt;&gt;"","szNote="""&amp;K35&amp;""",","")&amp;IF(L35&lt;&gt;"","col={"&amp;L35&amp;"},","")&amp;"[1]={"&amp;IF(M35&lt;&gt;"","tMark={"&amp;M35&amp;"},","")&amp;IF(N35&lt;&gt;"","szVoice="""&amp;N35&amp;""",","")&amp;IF(O35&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P35&gt;0,"bTeamChannel=true,","")&amp;IF(Q35&gt;0,"bWhisperChannel=true,","")&amp;IF(R35&gt;0,"bCenterAlarm=true,","")&amp;IF(S35&gt;0,"bScreenHead=true,","")&amp;IF(T35&gt;0,"bPartyBuffList=true,","")&amp;IF(U35&gt;0,"bBuffList=true,","")&amp;IF(V35&gt;0,"bFullScreen=true,","")&amp;IF(W35&gt;0,"bTeamPanel=true,","")&amp;IF(X35&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y35&lt;&gt;"","szVoice="""&amp;Y35&amp;""",","")&amp;IF(Z35&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA35&gt;0,"bTeamChannel=true,","")&amp;IF(AB35&gt;0,"bWhisperChannel=true,","")&amp;IF(AC35&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD35&gt;0,AH35&lt;&gt;"",AI35&gt;0,AJ35&lt;&gt;"",AK35&lt;&gt;"",AL35&gt;0,AM35&gt;0,AN35&gt;0,AO35&gt;0),"aCataclysmBuff={{"&amp;IF(AD35&gt;0,"nStackNum="&amp;AD35&amp;",","")&amp;IF(AE35&lt;&gt;"","szStackOp="""&amp;AE35&amp;""",","")&amp;IF(AF35&gt;0,"bOnlyMine=true,","")&amp;IF(AG35&gt;0,"bOnlyMe=true,","")&amp;IF(AH35&lt;&gt;"","szReminder="""&amp;AH35&amp;""",","")&amp;IF(AI35&gt;0,"nPriority="&amp;AI35&amp;",","")&amp;IF(AJ35&lt;&gt;"","col="""&amp;AJ35&amp;""",","")&amp;IF(AK35&lt;&gt;"","colScreenHead="""&amp;AK35&amp;""",","")&amp;IF(AL35&gt;0,"nColAlpha="&amp;AL35&amp;",","")&amp;IF(AM35&gt;0,"bAttention=true,","")&amp;IF(AN35&gt;0,"bCaution=true,","")&amp;IF(AO35&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP35&amp;"},","")&amp;IF(AR35&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR35:AAC35)&amp;"},","")&amp;"},",IF(C34&gt;0,"},","")&amp;IF(AND(B35="",C35="",OR(B34&lt;&gt;"",C34&lt;&gt;"")),"},}","")))</f>
-        <v>{dwID=27689,nLevel=1,nScrutinyType=1,szNote="缘会·今夕何夕",col={0,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=21596,nFrame=5,nTime=0,szName="缘会·今夕何夕",key="缘会·今夕何夕",},{nClass=2,nIcon=21596,nFrame=2,nTime=60,szName="香膏·绝世奇遇·已消失",key="缘会·今夕何夕",},},},</v>
-      </c>
-      <c r="AR35" s="1" t="s">
+        <v>{dwID=17365,nLevel=46,bCheckLevel=true,nScrutinyType=1,szNote="破招降低·无双提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·无双提高",key="创意食品",},},},</v>
+      </c>
+      <c r="AR35" t="s">
         <v>1582</v>
       </c>
-      <c r="AS35" s="1" t="s">
+    </row>
+    <row r="36" spans="3:44">
+      <c r="C36">
+        <v>17365</v>
+      </c>
+      <c r="D36">
+        <v>47</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="K36" t="s">
         <v>1583</v>
       </c>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="3:45">
-      <c r="C36" s="1">
-        <v>27663</v>
-      </c>
-      <c r="D36" s="1">
-        <v>1</v>
-      </c>
-      <c r="I36" s="1">
-        <v>1</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>1584</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>613</v>
+      <c r="L36" t="s">
+        <v>622</v>
       </c>
       <c r="AQ36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=27663,nLevel=1,nScrutinyType=1,szNote="缘会·月出皎兮",col={0,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=21600,nFrame=5,nTime=0,szName="缘会·月出皎兮",key="缘会·月出皎兮",},{nClass=2,nIcon=21600,nFrame=2,nTime=60,szName="香膏·普通奇遇·已消失",key="缘会·月出皎兮",},},},</v>
-      </c>
-      <c r="AR36" s="1" t="s">
+        <v>{dwID=17365,nLevel=47,bCheckLevel=true,nScrutinyType=1,szNote="破招降低·内攻提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·内攻提高",key="创意食品",},},},</v>
+      </c>
+      <c r="AR36" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="37" spans="3:44">
+      <c r="C37">
+        <v>17365</v>
+      </c>
+      <c r="D37">
+        <v>48</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="K37" t="s">
         <v>1585</v>
       </c>
-      <c r="AS36" s="1" t="s">
-        <v>1586</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="3:45">
-      <c r="C37" s="1">
-        <v>27662</v>
-      </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
-      <c r="I37" s="1">
-        <v>1</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>1587</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>613</v>
+      <c r="L37" t="s">
+        <v>622</v>
       </c>
       <c r="AQ37" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=27662,nLevel=1,nScrutinyType=1,szNote="缘会·山有扶苏",col={0,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=21600,nFrame=5,nTime=0,szName="缘会·山有扶苏",key="缘会·山有扶苏",},{nClass=2,nIcon=21600,nFrame=2,nTime=60,szName="香膏·宠物奇遇·已消失",key="缘会·山有扶苏",},},},</v>
-      </c>
-      <c r="AR37" s="1" t="s">
-        <v>1588</v>
-      </c>
-      <c r="AS37" s="1" t="s">
-        <v>1589</v>
-      </c>
-    </row>
-    <row r="38" spans="3:45">
+        <v>{dwID=17365,nLevel=48,bCheckLevel=true,nScrutinyType=1,szNote="破招降低·外攻提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·外攻提高",key="创意食品",},},},</v>
+      </c>
+      <c r="AR37" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="38" spans="3:44">
       <c r="C38">
         <v>17365</v>
       </c>
       <c r="D38">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -17666,25 +17660,25 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="L38" t="s">
         <v>622</v>
       </c>
       <c r="AQ38" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17365,nLevel=46,bCheckLevel=true,nScrutinyType=1,szNote="破招降低·无双提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·无双提高",key="创意食品",},},},</v>
+        <v>{dwID=17365,nLevel=49,bCheckLevel=true,nScrutinyType=1,szNote="破招降低·破防提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·破防提高",key="创意食品",},},},</v>
       </c>
       <c r="AR38" t="s">
-        <v>1591</v>
-      </c>
-    </row>
-    <row r="39" spans="3:45">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="39" spans="3:44">
       <c r="C39">
         <v>17365</v>
       </c>
       <c r="D39">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -17693,25 +17687,25 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="L39" t="s">
         <v>622</v>
       </c>
       <c r="AQ39" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17365,nLevel=47,bCheckLevel=true,nScrutinyType=1,szNote="破招降低·内攻提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·内攻提高",key="创意食品",},},},</v>
+        <v>{dwID=17365,nLevel=50,bCheckLevel=true,nScrutinyType=1,szNote="破招降低·会心提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·会心提高",key="创意食品",},},},</v>
       </c>
       <c r="AR39" t="s">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="40" spans="3:45">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="40" spans="3:44">
       <c r="C40">
         <v>17365</v>
       </c>
       <c r="D40">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -17720,25 +17714,25 @@
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="L40" t="s">
         <v>622</v>
       </c>
       <c r="AQ40" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17365,nLevel=48,bCheckLevel=true,nScrutinyType=1,szNote="破招降低·外攻提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·外攻提高",key="创意食品",},},},</v>
+        <v>{dwID=17365,nLevel=51,bCheckLevel=true,nScrutinyType=1,szNote="无双降低·破招提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·破招提高",key="创意食品",},},},</v>
       </c>
       <c r="AR40" t="s">
-        <v>1595</v>
-      </c>
-    </row>
-    <row r="41" spans="3:45">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="41" spans="3:44">
       <c r="C41">
         <v>17365</v>
       </c>
       <c r="D41">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -17747,25 +17741,25 @@
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="L41" t="s">
         <v>622</v>
       </c>
       <c r="AQ41" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17365,nLevel=49,bCheckLevel=true,nScrutinyType=1,szNote="破招降低·破防提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·破防提高",key="创意食品",},},},</v>
+        <v>{dwID=17365,nLevel=52,bCheckLevel=true,nScrutinyType=1,szNote="无双降低·内攻提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·内攻提高",key="创意食品",},},},</v>
       </c>
       <c r="AR41" t="s">
-        <v>1597</v>
-      </c>
-    </row>
-    <row r="42" spans="3:45">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="42" spans="3:44">
       <c r="C42">
         <v>17365</v>
       </c>
       <c r="D42">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -17774,25 +17768,25 @@
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="L42" t="s">
         <v>622</v>
       </c>
       <c r="AQ42" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17365,nLevel=50,bCheckLevel=true,nScrutinyType=1,szNote="破招降低·会心提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="破招降低·会心提高",key="创意食品",},},},</v>
+        <v>{dwID=17365,nLevel=53,bCheckLevel=true,nScrutinyType=1,szNote="无双降低·外攻提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·外攻提高",key="创意食品",},},},</v>
       </c>
       <c r="AR42" t="s">
-        <v>1599</v>
-      </c>
-    </row>
-    <row r="43" spans="3:45">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="43" spans="3:44">
       <c r="C43">
         <v>17365</v>
       </c>
       <c r="D43">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -17801,25 +17795,25 @@
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="L43" t="s">
         <v>622</v>
       </c>
       <c r="AQ43" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17365,nLevel=51,bCheckLevel=true,nScrutinyType=1,szNote="无双降低·破招提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·破招提高",key="创意食品",},},},</v>
+        <v>{dwID=17365,nLevel=54,bCheckLevel=true,nScrutinyType=1,szNote="无双降低·破防提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·破防提高",key="创意食品",},},},</v>
       </c>
       <c r="AR43" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="44" spans="3:45">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="44" spans="3:44">
       <c r="C44">
         <v>17365</v>
       </c>
       <c r="D44">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -17828,25 +17822,25 @@
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="L44" t="s">
         <v>622</v>
       </c>
       <c r="AQ44" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17365,nLevel=52,bCheckLevel=true,nScrutinyType=1,szNote="无双降低·内攻提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·内攻提高",key="创意食品",},},},</v>
+        <v>{dwID=17365,nLevel=55,bCheckLevel=true,nScrutinyType=1,szNote="无双降低·会心提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·会心提高",key="创意食品",},},},</v>
       </c>
       <c r="AR44" t="s">
-        <v>1603</v>
-      </c>
-    </row>
-    <row r="45" spans="3:45">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="45" spans="3:44">
       <c r="C45">
         <v>17365</v>
       </c>
       <c r="D45">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -17855,25 +17849,25 @@
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="L45" t="s">
         <v>622</v>
       </c>
       <c r="AQ45" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17365,nLevel=53,bCheckLevel=true,nScrutinyType=1,szNote="无双降低·外攻提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·外攻提高",key="创意食品",},},},</v>
+        <v>{dwID=17365,nLevel=56,bCheckLevel=true,nScrutinyType=1,szNote="气血降低·无双提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·无双提高",key="创意食品",},},},</v>
       </c>
       <c r="AR45" t="s">
-        <v>1605</v>
-      </c>
-    </row>
-    <row r="46" spans="3:45">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="46" spans="3:44">
       <c r="C46">
         <v>17365</v>
       </c>
       <c r="D46">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -17882,25 +17876,25 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="L46" t="s">
         <v>622</v>
       </c>
       <c r="AQ46" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17365,nLevel=54,bCheckLevel=true,nScrutinyType=1,szNote="无双降低·破防提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·破防提高",key="创意食品",},},},</v>
+        <v>{dwID=17365,nLevel=57,bCheckLevel=true,nScrutinyType=1,szNote="气血降低·内攻提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·内攻提高",key="创意食品",},},},</v>
       </c>
       <c r="AR46" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="47" spans="3:45">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="47" spans="3:44">
       <c r="C47">
         <v>17365</v>
       </c>
       <c r="D47">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -17909,25 +17903,25 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="L47" t="s">
         <v>622</v>
       </c>
       <c r="AQ47" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17365,nLevel=55,bCheckLevel=true,nScrutinyType=1,szNote="无双降低·会心提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="无双降低·会心提高",key="创意食品",},},},</v>
+        <v>{dwID=17365,nLevel=58,bCheckLevel=true,nScrutinyType=1,szNote="气血降低·外攻提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·外攻提高",key="创意食品",},},},</v>
       </c>
       <c r="AR47" t="s">
-        <v>1609</v>
-      </c>
-    </row>
-    <row r="48" spans="3:45">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="48" spans="3:44">
       <c r="C48">
         <v>17365</v>
       </c>
       <c r="D48">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -17936,17 +17930,17 @@
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="L48" t="s">
         <v>622</v>
       </c>
       <c r="AQ48" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17365,nLevel=56,bCheckLevel=true,nScrutinyType=1,szNote="气血降低·无双提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·无双提高",key="创意食品",},},},</v>
+        <v>{dwID=17365,nLevel=59,bCheckLevel=true,nScrutinyType=1,szNote="气血降低·破防提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·破防提高",key="创意食品",},},},</v>
       </c>
       <c r="AR48" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="49" spans="3:44">
@@ -17954,7 +17948,7 @@
         <v>17365</v>
       </c>
       <c r="D49">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -17963,166 +17957,169 @@
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="L49" t="s">
         <v>622</v>
       </c>
       <c r="AQ49" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17365,nLevel=57,bCheckLevel=true,nScrutinyType=1,szNote="气血降低·内攻提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·内攻提高",key="创意食品",},},},</v>
+        <v>{dwID=17365,nLevel=60,bCheckLevel=true,nScrutinyType=1,szNote="气血降低·会心提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·会心提高",key="创意食品",},},},</v>
       </c>
       <c r="AR49" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50">
-        <v>17365</v>
+        <v>30720</v>
       </c>
       <c r="D50">
-        <v>58</v>
-      </c>
-      <c r="H50">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="G50" t="s">
+        <v>1611</v>
       </c>
       <c r="I50">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="L50" t="s">
         <v>622</v>
       </c>
+      <c r="U50">
+        <v>1</v>
+      </c>
       <c r="AQ50" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17365,nLevel=58,bCheckLevel=true,nScrutinyType=1,szNote="气血降低·外攻提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·外攻提高",key="创意食品",},},},</v>
-      </c>
-      <c r="AR50" t="s">
-        <v>1615</v>
+        <v>{dwID=30720,nLevel=1,szName="鞋会心",nScrutinyType=1,szNote="PVP附魔2鞋子战阶_雷特效_太极秘录",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51">
-        <v>17365</v>
+        <v>30719</v>
       </c>
       <c r="D51">
-        <v>59</v>
-      </c>
-      <c r="H51">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="G51" t="s">
+        <v>1613</v>
       </c>
       <c r="I51">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="L51" t="s">
-        <v>622</v>
+        <v>1615</v>
       </c>
       <c r="AQ51" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17365,nLevel=59,bCheckLevel=true,nScrutinyType=1,szNote="气血降低·破防提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·破防提高",key="创意食品",},},},</v>
-      </c>
-      <c r="AR51" t="s">
-        <v>1617</v>
+        <v>{dwID=30719,nLevel=1,szName="鞋移速",nScrutinyType=1,szNote="PVP附魔1鞋子_移速",col={29,238,255,},[1]={},[2]={},},</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52">
-        <v>17365</v>
+        <v>30718</v>
       </c>
       <c r="D52">
-        <v>60</v>
-      </c>
-      <c r="H52">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="G52" t="s">
+        <v>1616</v>
       </c>
       <c r="I52">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="L52" t="s">
         <v>622</v>
       </c>
+      <c r="U52">
+        <v>1</v>
+      </c>
       <c r="AQ52" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17365,nLevel=60,bCheckLevel=true,nScrutinyType=1,szNote="气血降低·会心提高",col={0,255,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=549,nFrame=6,nTime=8,szName="气血降低·会心提高",key="创意食品",},},},</v>
-      </c>
-      <c r="AR52" t="s">
-        <v>1619</v>
+        <v>{dwID=30718,nLevel=1,szName="鞋伤疗",nScrutinyType=1,szNote="PVP附魔1鞋子战阶_水特效_太极秘录",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53">
-        <v>30720</v>
+        <v>30717</v>
       </c>
       <c r="D53">
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="I53">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="L53" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="U53">
         <v>1</v>
       </c>
       <c r="AQ53" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=30720,nLevel=1,szName="鞋会心",nScrutinyType=1,szNote="PVP附魔2鞋子战阶_雷特效_太极秘录",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=30717,nLevel=1,szName="衣护盾",nScrutinyType=1,szNote="PVP附魔2上衣_护盾_太极秘录",col={0,255,0,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54">
-        <v>30719</v>
+        <v>30716</v>
       </c>
       <c r="D54">
         <v>1</v>
       </c>
+      <c r="F54">
+        <v>19548</v>
+      </c>
       <c r="G54" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="I54">
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="L54" t="s">
-        <v>1624</v>
+        <v>1615</v>
+      </c>
+      <c r="U54">
+        <v>1</v>
       </c>
       <c r="AQ54" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=30719,nLevel=1,szName="鞋移速",nScrutinyType=1,szNote="PVP附魔1鞋子_移速",col={29,238,255,},[1]={},[2]={},},</v>
+        <v>{dwID=30716,nLevel=1,nIcon=19548,szName="衣恢复",nScrutinyType=1,szNote="PVP附魔1上衣战阶_持续回复效果_太极秘录",col={29,238,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55">
-        <v>30718</v>
+        <v>30709</v>
       </c>
       <c r="D55">
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
       <c r="I55">
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="L55" t="s">
         <v>622</v>
@@ -18132,81 +18129,75 @@
       </c>
       <c r="AQ55" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=30718,nLevel=1,szName="鞋伤疗",nScrutinyType=1,szNote="PVP附魔1鞋子战阶_水特效_太极秘录",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=30709,nLevel=1,szName="头特效",nScrutinyType=1,szNote="PVP附魔1帽子_密玉BUFF",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="56" spans="3:44">
       <c r="C56">
-        <v>30717</v>
+        <v>30708</v>
       </c>
       <c r="D56">
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="I56">
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="L56" t="s">
-        <v>613</v>
-      </c>
-      <c r="U56">
-        <v>1</v>
+        <v>622</v>
       </c>
       <c r="AQ56" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=30717,nLevel=1,szName="衣护盾",nScrutinyType=1,szNote="PVP附魔2上衣_护盾_太极秘录",col={0,255,0,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=30708,nLevel=1,szName="化转御",nScrutinyType=1,szNote="PVP附魔2腰带战阶_化劲转御劲_太极秘录",col={0,255,255,},[1]={},[2]={},},</v>
       </c>
     </row>
     <row r="57" spans="3:44">
       <c r="C57">
-        <v>30716</v>
+        <v>30707</v>
       </c>
       <c r="D57">
         <v>1</v>
       </c>
-      <c r="F57">
-        <v>19548</v>
-      </c>
       <c r="G57" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="I57">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="L57" t="s">
-        <v>1624</v>
+        <v>613</v>
       </c>
       <c r="U57">
         <v>1</v>
       </c>
       <c r="AQ57" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=30716,nLevel=1,nIcon=19548,szName="衣恢复",nScrutinyType=1,szNote="PVP附魔1上衣战阶_持续回复效果_太极秘录",col={29,238,255,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=30707,nLevel=1,szName="腰御劲",nScrutinyType=1,szNote="PVP附魔1腰带战阶_被击加御劲_太极秘录",col={0,255,0,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58">
-        <v>30709</v>
+        <v>30705</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="I58">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="L58" t="s">
         <v>622</v>
@@ -18216,48 +18207,54 @@
       </c>
       <c r="AQ58" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=30709,nLevel=1,szName="头特效",nScrutinyType=1,szNote="PVP附魔1帽子_密玉BUFF",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=30705,nLevel=1,szName="手会心",nScrutinyType=1,szNote="PVP附魔2护手战阶_全会心添加_太极秘录",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="59" spans="3:44">
       <c r="C59">
-        <v>30708</v>
+        <v>30703</v>
       </c>
       <c r="D59">
         <v>1</v>
       </c>
+      <c r="F59">
+        <v>23942</v>
+      </c>
       <c r="G59" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="I59">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="L59" t="s">
         <v>622</v>
       </c>
+      <c r="U59">
+        <v>1</v>
+      </c>
       <c r="AQ59" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=30708,nLevel=1,szName="化转御",nScrutinyType=1,szNote="PVP附魔2腰带战阶_化劲转御劲_太极秘录",col={0,255,255,},[1]={},[2]={},},</v>
+        <v>{dwID=30703,nLevel=1,nIcon=23942,szName="手特效",nScrutinyType=1,szNote="PVP附魔1护手拍卖_效果添加",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60">
-        <v>30707</v>
+        <v>30083</v>
       </c>
       <c r="D60">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="I60">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="L60" t="s">
         <v>613</v>
@@ -18267,168 +18264,168 @@
       </c>
       <c r="AQ60" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=30707,nLevel=1,szName="腰御劲",nScrutinyType=1,szNote="PVP附魔1腰带战阶_被击加御劲_太极秘录",col={0,255,0,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=30083,nLevel=1,szName="腰护盾",nScrutinyType=1,szNote="PVP腰带护盾",col={0,255,0,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61">
-        <v>30705</v>
+        <v>30073</v>
       </c>
       <c r="D61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>1637</v>
+        <v>1613</v>
       </c>
       <c r="I61">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>1638</v>
+        <v>1634</v>
       </c>
       <c r="L61" t="s">
-        <v>622</v>
+        <v>1615</v>
       </c>
       <c r="U61">
         <v>1</v>
       </c>
       <c r="AQ61" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=30705,nLevel=1,szName="手会心",nScrutinyType=1,szNote="PVP附魔2护手战阶_全会心添加_太极秘录",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=30073,nLevel=1,szName="鞋移速",nScrutinyType=1,szNote="PVP鞋子受击加移速20%",col={29,238,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62">
-        <v>30703</v>
+        <v>30072</v>
       </c>
       <c r="D62">
         <v>1</v>
       </c>
       <c r="F62">
-        <v>23942</v>
+        <v>16720</v>
       </c>
       <c r="G62" t="s">
-        <v>1639</v>
+        <v>1635</v>
       </c>
       <c r="I62">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>1640</v>
+        <v>1636</v>
       </c>
       <c r="L62" t="s">
-        <v>622</v>
+        <v>1615</v>
       </c>
       <c r="U62">
         <v>1</v>
       </c>
       <c r="AQ62" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=30703,nLevel=1,nIcon=23942,szName="手特效",nScrutinyType=1,szNote="PVP附魔1护手拍卖_效果添加",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=30072,nLevel=1,nIcon=16720,szName="裤治疗",nScrutinyType=1,szNote="治疗PVP裤子加治疗",col={29,238,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63">
-        <v>30083</v>
+        <v>30071</v>
       </c>
       <c r="D63">
         <v>1</v>
       </c>
+      <c r="F63">
+        <v>16717</v>
+      </c>
       <c r="G63" t="s">
-        <v>1641</v>
+        <v>1637</v>
       </c>
       <c r="I63">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>1642</v>
+        <v>1638</v>
       </c>
       <c r="L63" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="U63">
         <v>1</v>
       </c>
       <c r="AQ63" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=30083,nLevel=1,szName="腰护盾",nScrutinyType=1,szNote="PVP腰带护盾",col={0,255,0,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=30071,nLevel=1,nIcon=16717,szName="裤攻击",nScrutinyType=1,szNote="输出PVP裤子加攻击",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="64" spans="3:44">
       <c r="C64">
-        <v>30073</v>
+        <v>29268</v>
       </c>
       <c r="D64">
         <v>1</v>
       </c>
+      <c r="F64">
+        <v>4519</v>
+      </c>
       <c r="G64" t="s">
-        <v>1622</v>
+        <v>1639</v>
       </c>
       <c r="I64">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="L64" t="s">
-        <v>1624</v>
+        <v>622</v>
       </c>
       <c r="U64">
         <v>1</v>
       </c>
       <c r="AQ64" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=30073,nLevel=1,szName="鞋移速",nScrutinyType=1,szNote="PVP鞋子受击加移速20%",col={29,238,255,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=29268,nLevel=1,nIcon=4519,szName="风腰坠",nScrutinyType=1,szNote="PVP风·斩流",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="65" spans="1:45">
       <c r="C65">
-        <v>30072</v>
+        <v>3067</v>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
-      <c r="F65">
-        <v>16720</v>
-      </c>
-      <c r="G65" t="s">
-        <v>1644</v>
-      </c>
       <c r="I65">
         <v>1</v>
       </c>
+      <c r="J65" t="s">
+        <v>1641</v>
+      </c>
       <c r="K65" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="L65" t="s">
-        <v>1624</v>
+        <v>1615</v>
       </c>
       <c r="U65">
         <v>1</v>
       </c>
       <c r="AQ65" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=30072,nLevel=1,nIcon=16720,szName="裤治疗",nScrutinyType=1,szNote="治疗PVP裤子加治疗",col={29,238,255,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=3067,nLevel=1,nScrutinyType=1,tKungFu={["SKILL#10028"]=true,["SKILL#10080"]=true,["SKILL#10176"]=true,["SKILL#10448"]=true,["SKILL#10626"]=true,},szNote="沐风-基础治疗量提高",col={29,238,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="66" spans="1:45">
       <c r="C66">
-        <v>30071</v>
+        <v>4761</v>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
-      <c r="F66">
-        <v>16717</v>
-      </c>
       <c r="G66" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
       <c r="I66">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
       <c r="L66" t="s">
         <v>622</v>
@@ -18438,27 +18435,24 @@
       </c>
       <c r="AQ66" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=30071,nLevel=1,nIcon=16717,szName="裤攻击",nScrutinyType=1,szNote="输出PVP裤子加攻击",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=4761,nLevel=1,szName="水武器",nScrutinyType=1,szNote="水·鋭刃-水特效武器",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="67" spans="1:45">
       <c r="C67">
-        <v>29268</v>
+        <v>4759</v>
       </c>
       <c r="D67">
         <v>1</v>
       </c>
-      <c r="F67">
-        <v>4519</v>
-      </c>
       <c r="G67" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
       <c r="I67">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="L67" t="s">
         <v>622</v>
@@ -18467,136 +18461,118 @@
         <v>1</v>
       </c>
       <c r="AQ67" t="str">
-        <f t="shared" ref="AQ67:AQ98" si="2">IF(B67&lt;&gt;"",IF(IFERROR(VALUE(C66),0)&lt;=0,"["&amp;B67&amp;"]={","},["&amp;B67&amp;"]={"),IF(C67&gt;0,"{dwID="&amp;C67&amp;","&amp;"nLevel="&amp;D67&amp;","&amp;IF(E67&gt;0,"nCount="&amp;E67&amp;",","")&amp;IF(F67&gt;0,"nIcon="&amp;F67&amp;",","")&amp;IF(G67&lt;&gt;"","szName="""&amp;G67&amp;""",","")&amp;IF(H67&gt;0,"bCheckLevel=true,","")&amp;IF(I67&gt;0,"nScrutinyType="&amp;I67&amp;",","")&amp;IF(J67&lt;&gt;"","tKungFu={"&amp;J67&amp;"},","")&amp;IF(K67&lt;&gt;"","szNote="""&amp;K67&amp;""",","")&amp;IF(L67&lt;&gt;"","col={"&amp;L67&amp;"},","")&amp;"[1]={"&amp;IF(M67&lt;&gt;"","tMark={"&amp;M67&amp;"},","")&amp;IF(N67&lt;&gt;"","szVoice="""&amp;N67&amp;""",","")&amp;IF(O67&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P67&gt;0,"bTeamChannel=true,","")&amp;IF(Q67&gt;0,"bWhisperChannel=true,","")&amp;IF(R67&gt;0,"bCenterAlarm=true,","")&amp;IF(S67&gt;0,"bScreenHead=true,","")&amp;IF(T67&gt;0,"bPartyBuffList=true,","")&amp;IF(U67&gt;0,"bBuffList=true,","")&amp;IF(V67&gt;0,"bFullScreen=true,","")&amp;IF(W67&gt;0,"bTeamPanel=true,","")&amp;IF(X67&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y67&lt;&gt;"","szVoice="""&amp;Y67&amp;""",","")&amp;IF(Z67&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA67&gt;0,"bTeamChannel=true,","")&amp;IF(AB67&gt;0,"bWhisperChannel=true,","")&amp;IF(AC67&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD67&gt;0,AH67&lt;&gt;"",AI67&gt;0,AJ67&lt;&gt;"",AK67&lt;&gt;"",AL67&gt;0,AM67&gt;0,AN67&gt;0,AO67&gt;0),"aCataclysmBuff={{"&amp;IF(AD67&gt;0,"nStackNum="&amp;AD67&amp;",","")&amp;IF(AE67&lt;&gt;"","szStackOp="""&amp;AE67&amp;""",","")&amp;IF(AF67&gt;0,"bOnlyMine=true,","")&amp;IF(AG67&gt;0,"bOnlyMe=true,","")&amp;IF(AH67&lt;&gt;"","szReminder="""&amp;AH67&amp;""",","")&amp;IF(AI67&gt;0,"nPriority="&amp;AI67&amp;",","")&amp;IF(AJ67&lt;&gt;"","col="""&amp;AJ67&amp;""",","")&amp;IF(AK67&lt;&gt;"","colScreenHead="""&amp;AK67&amp;""",","")&amp;IF(AL67&gt;0,"nColAlpha="&amp;AL67&amp;",","")&amp;IF(AM67&gt;0,"bAttention=true,","")&amp;IF(AN67&gt;0,"bCaution=true,","")&amp;IF(AO67&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP67&amp;"},","")&amp;IF(AR67&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR67:AAC67)&amp;"},","")&amp;"},",IF(C66&gt;0,"},","")&amp;IF(AND(B67="",C67="",OR(B66&lt;&gt;"",C66&lt;&gt;"")),"},}","")))</f>
-        <v>{dwID=29268,nLevel=1,nIcon=4519,szName="风腰坠",nScrutinyType=1,szNote="PVP风·斩流",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
+        <f t="shared" ref="AQ67:AQ96" si="2">IF(B67&lt;&gt;"",IF(IFERROR(VALUE(C66),0)&lt;=0,"["&amp;B67&amp;"]={","},["&amp;B67&amp;"]={"),IF(C67&gt;0,"{dwID="&amp;C67&amp;","&amp;"nLevel="&amp;D67&amp;","&amp;IF(E67&gt;0,"nCount="&amp;E67&amp;",","")&amp;IF(F67&gt;0,"nIcon="&amp;F67&amp;",","")&amp;IF(G67&lt;&gt;"","szName="""&amp;G67&amp;""",","")&amp;IF(H67&gt;0,"bCheckLevel=true,","")&amp;IF(I67&gt;0,"nScrutinyType="&amp;I67&amp;",","")&amp;IF(J67&lt;&gt;"","tKungFu={"&amp;J67&amp;"},","")&amp;IF(K67&lt;&gt;"","szNote="""&amp;K67&amp;""",","")&amp;IF(L67&lt;&gt;"","col={"&amp;L67&amp;"},","")&amp;"[1]={"&amp;IF(M67&lt;&gt;"","tMark={"&amp;M67&amp;"},","")&amp;IF(N67&lt;&gt;"","szVoice="""&amp;N67&amp;""",","")&amp;IF(O67&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P67&gt;0,"bTeamChannel=true,","")&amp;IF(Q67&gt;0,"bWhisperChannel=true,","")&amp;IF(R67&gt;0,"bCenterAlarm=true,","")&amp;IF(S67&gt;0,"bScreenHead=true,","")&amp;IF(T67&gt;0,"bPartyBuffList=true,","")&amp;IF(U67&gt;0,"bBuffList=true,","")&amp;IF(V67&gt;0,"bFullScreen=true,","")&amp;IF(W67&gt;0,"bTeamPanel=true,","")&amp;IF(X67&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y67&lt;&gt;"","szVoice="""&amp;Y67&amp;""",","")&amp;IF(Z67&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA67&gt;0,"bTeamChannel=true,","")&amp;IF(AB67&gt;0,"bWhisperChannel=true,","")&amp;IF(AC67&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD67&gt;0,AH67&lt;&gt;"",AI67&gt;0,AJ67&lt;&gt;"",AK67&lt;&gt;"",AL67&gt;0,AM67&gt;0,AN67&gt;0,AO67&gt;0),"aCataclysmBuff={{"&amp;IF(AD67&gt;0,"nStackNum="&amp;AD67&amp;",","")&amp;IF(AE67&lt;&gt;"","szStackOp="""&amp;AE67&amp;""",","")&amp;IF(AF67&gt;0,"bOnlyMine=true,","")&amp;IF(AG67&gt;0,"bOnlyMe=true,","")&amp;IF(AH67&lt;&gt;"","szReminder="""&amp;AH67&amp;""",","")&amp;IF(AI67&gt;0,"nPriority="&amp;AI67&amp;",","")&amp;IF(AJ67&lt;&gt;"","col="""&amp;AJ67&amp;""",","")&amp;IF(AK67&lt;&gt;"","colScreenHead="""&amp;AK67&amp;""",","")&amp;IF(AL67&gt;0,"nColAlpha="&amp;AL67&amp;",","")&amp;IF(AM67&gt;0,"bAttention=true,","")&amp;IF(AN67&gt;0,"bCaution=true,","")&amp;IF(AO67&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP67&amp;"},","")&amp;IF(AR67&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR67:AAC67)&amp;"},","")&amp;"},",IF(C66&gt;0,"},","")&amp;IF(AND(B67="",C67="",OR(B66&lt;&gt;"",C66&lt;&gt;"")),"},}","")))</f>
+        <v>{dwID=4759,nLevel=1,szName="雷武器",nScrutinyType=1,szNote="雷·鋭刃-雷特效武器",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="68" spans="1:45">
       <c r="C68">
-        <v>3067</v>
+        <v>6360</v>
       </c>
       <c r="D68">
         <v>1</v>
       </c>
+      <c r="F68">
+        <v>4519</v>
+      </c>
+      <c r="G68" t="s">
+        <v>1639</v>
+      </c>
       <c r="I68">
         <v>1</v>
       </c>
-      <c r="J68" t="s">
-        <v>1650</v>
-      </c>
       <c r="K68" t="s">
-        <v>1651</v>
+        <v>1647</v>
       </c>
       <c r="L68" t="s">
-        <v>1624</v>
+        <v>622</v>
       </c>
       <c r="U68">
         <v>1</v>
       </c>
       <c r="AQ68" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=3067,nLevel=1,nScrutinyType=1,tKungFu={["SKILL#10028"]=true,["SKILL#10080"]=true,["SKILL#10176"]=true,["SKILL#10448"]=true,["SKILL#10626"]=true,},szNote="沐风-基础治疗量提高",col={29,238,255,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=6360,nLevel=1,nIcon=4519,szName="风腰坠",nScrutinyType=1,szNote="风·鋭刃-风特效腰坠",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="69" spans="1:45">
-      <c r="C69">
-        <v>4761</v>
-      </c>
-      <c r="D69">
-        <v>1</v>
-      </c>
-      <c r="G69" t="s">
-        <v>1652</v>
-      </c>
-      <c r="I69">
-        <v>1</v>
-      </c>
-      <c r="K69" t="s">
-        <v>1653</v>
-      </c>
-      <c r="L69" t="s">
-        <v>622</v>
-      </c>
-      <c r="U69">
-        <v>1</v>
+      <c r="A69" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B69">
+        <v>-3</v>
       </c>
       <c r="AQ69" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=4761,nLevel=1,szName="水武器",nScrutinyType=1,szNote="水·鋭刃-水特效武器",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
-      </c>
-    </row>
-    <row r="70" spans="1:45">
+        <v>},[-3]={</v>
+      </c>
+    </row>
+    <row r="70" customFormat="1" spans="1:45">
       <c r="C70">
-        <v>4759</v>
+        <v>2564</v>
       </c>
       <c r="D70">
         <v>1</v>
       </c>
-      <c r="G70" t="s">
-        <v>1654</v>
-      </c>
       <c r="I70">
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>1655</v>
-      </c>
-      <c r="L70" t="s">
-        <v>622</v>
-      </c>
-      <c r="U70">
-        <v>1</v>
+        <v>1649</v>
       </c>
       <c r="AQ70" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=4759,nLevel=1,szName="雷武器",nScrutinyType=1,szNote="雷·鋭刃-雷特效武器",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
-      </c>
-    </row>
-    <row r="71" spans="1:45">
+        <v>{dwID=2564,nLevel=1,nScrutinyType=1,szNote="肘子菜盘",[1]={},[2]={},tCountdown={{nClass=2,nIcon=546,nFrame=5,nTime=2,szName="肘子菜盘·消失",nRefresh=60,key="帮会外食",},},},</v>
+      </c>
+      <c r="AR70" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="71" customFormat="1" spans="1:45">
       <c r="C71">
-        <v>6360</v>
+        <v>2562</v>
       </c>
       <c r="D71">
         <v>1</v>
       </c>
-      <c r="F71">
-        <v>4519</v>
-      </c>
-      <c r="G71" t="s">
-        <v>1648</v>
-      </c>
       <c r="I71">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>1656</v>
-      </c>
-      <c r="L71" t="s">
-        <v>622</v>
-      </c>
-      <c r="U71">
-        <v>1</v>
+        <v>1651</v>
       </c>
       <c r="AQ71" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=6360,nLevel=1,nIcon=4519,szName="风腰坠",nScrutinyType=1,szNote="风·鋭刃-风特效腰坠",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
-      </c>
-    </row>
-    <row r="72" spans="1:45">
-      <c r="A72" t="s">
-        <v>1657</v>
-      </c>
-      <c r="B72">
-        <v>-3</v>
+        <v>{dwID=2562,nLevel=1,nScrutinyType=1,szNote="南瓜盅菜盘",[1]={},[2]={},tCountdown={{nClass=2,nIcon=1546,nFrame=5,nTime=3,szName="南瓜盅菜盘·消失",nRefresh=60,key="帮会外食",},},},</v>
+      </c>
+      <c r="AR71" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="72" customFormat="1" spans="1:45">
+      <c r="C72">
+        <v>17963</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="K72" t="s">
+        <v>1653</v>
       </c>
       <c r="AQ72" t="str">
         <f t="shared" si="2"/>
-        <v>},[-3]={</v>
+        <v>{dwID=17963,nLevel=1,nScrutinyType=1,szNote="烧鸡外食",[1]={},[2]={},tCountdown={{nClass=2,nIcon=171,nFrame=5,nTime=2,szName="烧鸡外食·消失",nRefresh=60,key="帮会外食",},},},</v>
+      </c>
+      <c r="AR72" t="s">
+        <v>1654</v>
       </c>
     </row>
     <row r="73" customFormat="1" spans="1:45">
       <c r="C73">
-        <v>2564</v>
+        <v>2563</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -18605,19 +18581,19 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>1658</v>
+        <v>1655</v>
       </c>
       <c r="AQ73" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=2564,nLevel=1,nScrutinyType=1,szNote="肘子菜盘",[1]={},[2]={},tCountdown={{nClass=2,nIcon=546,nFrame=5,nTime=2,szName="肘子菜盘·消失",nRefresh=60,key="帮会外食",},},},</v>
+        <v>{dwID=2563,nLevel=1,nScrutinyType=1,szNote="蒸鱼菜盘",[1]={},[2]={},tCountdown={{nClass=2,nIcon=552,nFrame=5,nTime=3,szName="蒸鱼菜盘·消失",nRefresh=60,key="帮会外食",},},},</v>
       </c>
       <c r="AR73" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="74" customFormat="1" spans="1:45">
       <c r="C74">
-        <v>2562</v>
+        <v>2560</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -18626,151 +18602,199 @@
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
       <c r="AQ74" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=2562,nLevel=1,nScrutinyType=1,szNote="南瓜盅菜盘",[1]={},[2]={},tCountdown={{nClass=2,nIcon=1546,nFrame=5,nTime=3,szName="南瓜盅菜盘·消失",nRefresh=60,key="帮会外食",},},},</v>
+        <v>{dwID=2560,nLevel=1,nScrutinyType=1,szNote="鸡肉菜盘",[1]={},[2]={},tCountdown={{nClass=1,nIcon=264,nFrame=5,nTime=2,szName="已食用·鸡肉菜盘5%",nRefresh=5,key="绣球花",},{nClass=2,nIcon=264,nFrame=5,nTime=2,szName="鸡肉菜盘·已消失",key="绣球花",},},},</v>
       </c>
       <c r="AR74" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AS74" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="75" spans="1:45">
+      <c r="C75">
+        <v>20398</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="K75" t="s">
+        <v>1660</v>
+      </c>
+      <c r="L75" t="s">
+        <v>613</v>
+      </c>
+      <c r="U75">
+        <v>1</v>
+      </c>
+      <c r="W75">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="s">
         <v>1661</v>
       </c>
-    </row>
-    <row r="75" customFormat="1" spans="1:45">
-      <c r="C75">
-        <v>17963</v>
-      </c>
-      <c r="D75">
-        <v>1</v>
-      </c>
-      <c r="I75">
-        <v>1</v>
-      </c>
-      <c r="K75" t="s">
+      <c r="AI75">
+        <v>11</v>
+      </c>
+      <c r="AJ75" t="s">
         <v>1662</v>
+      </c>
+      <c r="AK75" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AL75">
+        <v>255</v>
       </c>
       <c r="AQ75" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=17963,nLevel=1,nScrutinyType=1,szNote="烧鸡外食",[1]={},[2]={},tCountdown={{nClass=2,nIcon=171,nFrame=5,nTime=2,szName="烧鸡外食·消失",nRefresh=60,key="帮会外食",},},},</v>
+        <v>{dwID=20398,nLevel=1,szNote="龙葵",col={0,255,0,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="葵",nPriority=11,col="#00FF00FF",colScreenHead="#00FF00",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=15413,nFrame=6,nTime=7,szName="龙葵自苦·[{$sender}]",key="减伤监控",},},},</v>
       </c>
       <c r="AR75" t="s">
-        <v>1663</v>
-      </c>
-    </row>
-    <row r="76" customFormat="1" spans="1:45">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="76" spans="1:45">
       <c r="C76">
-        <v>2563</v>
+        <v>5693</v>
       </c>
       <c r="D76">
         <v>1</v>
       </c>
-      <c r="I76">
-        <v>1</v>
-      </c>
       <c r="K76" t="s">
-        <v>1664</v>
+        <v>1665</v>
+      </c>
+      <c r="W76">
+        <v>1</v>
+      </c>
+      <c r="X76">
+        <v>1</v>
+      </c>
+      <c r="AF76">
+        <v>1</v>
+      </c>
+      <c r="AH76" t="s">
+        <v>1666</v>
+      </c>
+      <c r="AI76">
+        <v>6</v>
+      </c>
+      <c r="AJ76" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AL76">
+        <v>255</v>
+      </c>
+      <c r="AM76">
+        <v>1</v>
       </c>
       <c r="AQ76" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=2563,nLevel=1,nScrutinyType=1,szNote="蒸鱼菜盘",[1]={},[2]={},tCountdown={{nClass=2,nIcon=552,nFrame=5,nTime=3,szName="蒸鱼菜盘·消失",nRefresh=60,key="帮会外食",},},},</v>
-      </c>
-      <c r="AR76" t="s">
-        <v>1665</v>
-      </c>
-    </row>
-    <row r="77" customFormat="1" spans="1:45">
+        <v>{dwID=5693,nLevel=1,szNote="述怀",[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="述",nPriority=6,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="77" spans="1:45">
       <c r="C77">
-        <v>2560</v>
+        <v>680</v>
       </c>
       <c r="D77">
         <v>1</v>
       </c>
-      <c r="I77">
-        <v>1</v>
-      </c>
       <c r="K77" t="s">
-        <v>1666</v>
+        <v>1668</v>
+      </c>
+      <c r="W77">
+        <v>1</v>
+      </c>
+      <c r="X77">
+        <v>1</v>
+      </c>
+      <c r="AF77">
+        <v>1</v>
+      </c>
+      <c r="AH77" t="s">
+        <v>1669</v>
+      </c>
+      <c r="AI77">
+        <v>5</v>
+      </c>
+      <c r="AJ77" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AL77">
+        <v>255</v>
+      </c>
+      <c r="AM77">
+        <v>1</v>
       </c>
       <c r="AQ77" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=2560,nLevel=1,nScrutinyType=1,szNote="鸡肉菜盘",[1]={},[2]={},tCountdown={{nClass=1,nIcon=264,nFrame=5,nTime=2,szName="已食用·鸡肉菜盘5%",nRefresh=5,key="绣球花",},{nClass=2,nIcon=264,nFrame=5,nTime=2,szName="鸡肉菜盘·已消失",key="绣球花",},},},</v>
-      </c>
-      <c r="AR77" t="s">
-        <v>1667</v>
-      </c>
-      <c r="AS77" t="s">
-        <v>1668</v>
+        <v>{dwID=680,nLevel=1,szNote="翔舞",[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="翔",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
       </c>
     </row>
     <row r="78" spans="1:45">
       <c r="C78">
-        <v>20398</v>
+        <v>681</v>
       </c>
       <c r="D78">
         <v>1</v>
       </c>
       <c r="K78" t="s">
-        <v>1669</v>
-      </c>
-      <c r="L78" t="s">
-        <v>613</v>
-      </c>
-      <c r="U78">
-        <v>1</v>
+        <v>1670</v>
       </c>
       <c r="W78">
         <v>1</v>
       </c>
+      <c r="X78">
+        <v>1</v>
+      </c>
+      <c r="AF78">
+        <v>1</v>
+      </c>
       <c r="AH78" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="AI78">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AJ78" t="s">
-        <v>1671</v>
-      </c>
-      <c r="AK78" t="s">
-        <v>1672</v>
+        <v>1667</v>
       </c>
       <c r="AL78">
         <v>255</v>
       </c>
+      <c r="AM78">
+        <v>1</v>
+      </c>
       <c r="AQ78" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=20398,nLevel=1,szNote="龙葵",col={0,255,0,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="葵",nPriority=11,col="#00FF00FF",colScreenHead="#00FF00",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=15413,nFrame=6,nTime=7,szName="龙葵自苦·[{$sender}]",key="减伤监控",},},},</v>
-      </c>
-      <c r="AR78" t="s">
-        <v>1673</v>
+        <v>{dwID=681,nLevel=1,szNote="上元点鬟",[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="元",nPriority=6,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
       </c>
     </row>
     <row r="79" spans="1:45">
       <c r="C79">
-        <v>5693</v>
+        <v>20070</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>1674</v>
-      </c>
-      <c r="W79">
-        <v>1</v>
-      </c>
-      <c r="X79">
-        <v>1</v>
+        <v>1672</v>
       </c>
       <c r="AF79">
         <v>1</v>
       </c>
       <c r="AH79" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="AI79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ79" t="s">
-        <v>1676</v>
+        <v>1667</v>
       </c>
       <c r="AL79">
         <v>255</v>
@@ -18780,36 +18804,33 @@
       </c>
       <c r="AQ79" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=5693,nLevel=1,szNote="述怀",[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="述",nPriority=6,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+        <v>{dwID=20070,nLevel=1,szNote="赤芍寒香",[1]={},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="芍",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
       </c>
     </row>
     <row r="80" spans="1:45">
       <c r="C80">
-        <v>680</v>
+        <v>9334</v>
       </c>
       <c r="D80">
         <v>1</v>
       </c>
       <c r="K80" t="s">
+        <v>1674</v>
+      </c>
+      <c r="L80" t="s">
+        <v>1675</v>
+      </c>
+      <c r="AF80">
+        <v>1</v>
+      </c>
+      <c r="AH80" t="s">
+        <v>1676</v>
+      </c>
+      <c r="AI80">
+        <v>4</v>
+      </c>
+      <c r="AJ80" t="s">
         <v>1677</v>
-      </c>
-      <c r="W80">
-        <v>1</v>
-      </c>
-      <c r="X80">
-        <v>1</v>
-      </c>
-      <c r="AF80">
-        <v>1</v>
-      </c>
-      <c r="AH80" t="s">
-        <v>1678</v>
-      </c>
-      <c r="AI80">
-        <v>5</v>
-      </c>
-      <c r="AJ80" t="s">
-        <v>1676</v>
       </c>
       <c r="AL80">
         <v>255</v>
@@ -18819,18 +18840,21 @@
       </c>
       <c r="AQ80" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=680,nLevel=1,szNote="翔舞",[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="翔",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="81" spans="3:43">
+        <v>{dwID=9334,nLevel=1,szNote="梅花三弄",col={31,255,238,},[1]={},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="梅",nPriority=4,col="#1FFFEEFF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="81" spans="1:43">
       <c r="C81">
-        <v>681</v>
+        <v>9454</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>1679</v>
+        <v>1678</v>
+      </c>
+      <c r="L81" t="s">
+        <v>613</v>
       </c>
       <c r="W81">
         <v>1</v>
@@ -18842,13 +18866,13 @@
         <v>1</v>
       </c>
       <c r="AH81" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="AI81">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ81" t="s">
-        <v>1676</v>
+        <v>1667</v>
       </c>
       <c r="AL81">
         <v>255</v>
@@ -18858,30 +18882,39 @@
       </c>
       <c r="AQ81" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=681,nLevel=1,szNote="上元点鬟",[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="元",nPriority=6,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="82" spans="3:43">
+        <v>{dwID=9454,nLevel=1,szNote="宫",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="宫",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="82" spans="1:43">
       <c r="C82">
-        <v>20070</v>
+        <v>9455</v>
       </c>
       <c r="D82">
         <v>1</v>
       </c>
       <c r="K82" t="s">
-        <v>1681</v>
+        <v>1678</v>
+      </c>
+      <c r="L82" t="s">
+        <v>613</v>
+      </c>
+      <c r="W82">
+        <v>1</v>
+      </c>
+      <c r="X82">
+        <v>1</v>
       </c>
       <c r="AF82">
         <v>1</v>
       </c>
       <c r="AH82" t="s">
-        <v>1682</v>
+        <v>1678</v>
       </c>
       <c r="AI82">
         <v>5</v>
       </c>
       <c r="AJ82" t="s">
-        <v>1676</v>
+        <v>1667</v>
       </c>
       <c r="AL82">
         <v>255</v>
@@ -18891,33 +18924,39 @@
       </c>
       <c r="AQ82" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=20070,nLevel=1,szNote="赤芍寒香",[1]={},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="芍",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="83" spans="3:43">
+        <v>{dwID=9455,nLevel=1,szNote="宫",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="宫",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="83" spans="1:43">
       <c r="C83">
-        <v>9334</v>
+        <v>9456</v>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="K83" t="s">
-        <v>1683</v>
+        <v>1678</v>
       </c>
       <c r="L83" t="s">
-        <v>1684</v>
+        <v>613</v>
+      </c>
+      <c r="W83">
+        <v>1</v>
+      </c>
+      <c r="X83">
+        <v>1</v>
       </c>
       <c r="AF83">
         <v>1</v>
       </c>
       <c r="AH83" t="s">
-        <v>1685</v>
+        <v>1678</v>
       </c>
       <c r="AI83">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ83" t="s">
-        <v>1686</v>
+        <v>1667</v>
       </c>
       <c r="AL83">
         <v>255</v>
@@ -18927,18 +18966,18 @@
       </c>
       <c r="AQ83" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=9334,nLevel=1,szNote="梅花三弄",col={31,255,238,},[1]={},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="梅",nPriority=4,col="#1FFFEEFF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="84" spans="3:43">
+        <v>{dwID=9456,nLevel=1,szNote="宫",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="宫",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="84" spans="1:43">
       <c r="C84">
-        <v>9454</v>
+        <v>9457</v>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>1687</v>
+        <v>1678</v>
       </c>
       <c r="L84" t="s">
         <v>613</v>
@@ -18953,13 +18992,13 @@
         <v>1</v>
       </c>
       <c r="AH84" t="s">
-        <v>1687</v>
+        <v>1678</v>
       </c>
       <c r="AI84">
         <v>5</v>
       </c>
       <c r="AJ84" t="s">
-        <v>1676</v>
+        <v>1667</v>
       </c>
       <c r="AL84">
         <v>255</v>
@@ -18969,18 +19008,18 @@
       </c>
       <c r="AQ84" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=9454,nLevel=1,szNote="宫",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="宫",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="85" spans="3:43">
+        <v>{dwID=9457,nLevel=1,szNote="宫",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="宫",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="85" spans="1:43">
       <c r="C85">
-        <v>9455</v>
+        <v>9459</v>
       </c>
       <c r="D85">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>1687</v>
+        <v>1679</v>
       </c>
       <c r="L85" t="s">
         <v>613</v>
@@ -18995,13 +19034,13 @@
         <v>1</v>
       </c>
       <c r="AH85" t="s">
-        <v>1687</v>
+        <v>1679</v>
       </c>
       <c r="AI85">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ85" t="s">
-        <v>1676</v>
+        <v>1667</v>
       </c>
       <c r="AL85">
         <v>255</v>
@@ -19011,18 +19050,18 @@
       </c>
       <c r="AQ85" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=9455,nLevel=1,szNote="宫",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="宫",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="86" spans="3:43">
+        <v>{dwID=9459,nLevel=1,szNote="商",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="商",nPriority=6,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="86" spans="1:43">
       <c r="C86">
-        <v>9456</v>
+        <v>9460</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>1687</v>
+        <v>1679</v>
       </c>
       <c r="L86" t="s">
         <v>613</v>
@@ -19037,13 +19076,13 @@
         <v>1</v>
       </c>
       <c r="AH86" t="s">
-        <v>1687</v>
+        <v>1679</v>
       </c>
       <c r="AI86">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ86" t="s">
-        <v>1676</v>
+        <v>1667</v>
       </c>
       <c r="AL86">
         <v>255</v>
@@ -19053,18 +19092,18 @@
       </c>
       <c r="AQ86" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=9456,nLevel=1,szNote="宫",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="宫",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="87" spans="3:43">
+        <v>{dwID=9460,nLevel=1,szNote="商",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="商",nPriority=6,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="87" spans="1:43">
       <c r="C87">
-        <v>9457</v>
+        <v>9461</v>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>1687</v>
+        <v>1679</v>
       </c>
       <c r="L87" t="s">
         <v>613</v>
@@ -19079,13 +19118,13 @@
         <v>1</v>
       </c>
       <c r="AH87" t="s">
-        <v>1687</v>
+        <v>1679</v>
       </c>
       <c r="AI87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ87" t="s">
-        <v>1676</v>
+        <v>1667</v>
       </c>
       <c r="AL87">
         <v>255</v>
@@ -19095,18 +19134,18 @@
       </c>
       <c r="AQ87" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=9457,nLevel=1,szNote="宫",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="宫",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="88" spans="3:43">
+        <v>{dwID=9461,nLevel=1,szNote="商",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="商",nPriority=6,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="88" spans="1:43">
       <c r="C88">
-        <v>9459</v>
+        <v>9462</v>
       </c>
       <c r="D88">
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>1688</v>
+        <v>1679</v>
       </c>
       <c r="L88" t="s">
         <v>613</v>
@@ -19121,13 +19160,13 @@
         <v>1</v>
       </c>
       <c r="AH88" t="s">
-        <v>1688</v>
+        <v>1679</v>
       </c>
       <c r="AI88">
         <v>6</v>
       </c>
       <c r="AJ88" t="s">
-        <v>1676</v>
+        <v>1667</v>
       </c>
       <c r="AL88">
         <v>255</v>
@@ -19137,18 +19176,18 @@
       </c>
       <c r="AQ88" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=9459,nLevel=1,szNote="商",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="商",nPriority=6,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="89" spans="3:43">
+        <v>{dwID=9462,nLevel=1,szNote="商",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="商",nPriority=6,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="89" spans="1:43">
       <c r="C89">
-        <v>9460</v>
+        <v>9463</v>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="K89" t="s">
-        <v>1688</v>
+        <v>1680</v>
       </c>
       <c r="L89" t="s">
         <v>613</v>
@@ -19163,13 +19202,13 @@
         <v>1</v>
       </c>
       <c r="AH89" t="s">
-        <v>1688</v>
+        <v>1680</v>
       </c>
       <c r="AI89">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ89" t="s">
-        <v>1676</v>
+        <v>1667</v>
       </c>
       <c r="AL89">
         <v>255</v>
@@ -19179,18 +19218,18 @@
       </c>
       <c r="AQ89" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=9460,nLevel=1,szNote="商",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="商",nPriority=6,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="90" spans="3:43">
+        <v>{dwID=9463,nLevel=1,szNote="角",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="角",nPriority=7,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="90" spans="1:43">
       <c r="C90">
-        <v>9461</v>
+        <v>9464</v>
       </c>
       <c r="D90">
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>1688</v>
+        <v>1680</v>
       </c>
       <c r="L90" t="s">
         <v>613</v>
@@ -19205,13 +19244,13 @@
         <v>1</v>
       </c>
       <c r="AH90" t="s">
-        <v>1688</v>
+        <v>1680</v>
       </c>
       <c r="AI90">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ90" t="s">
-        <v>1676</v>
+        <v>1667</v>
       </c>
       <c r="AL90">
         <v>255</v>
@@ -19221,18 +19260,18 @@
       </c>
       <c r="AQ90" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=9461,nLevel=1,szNote="商",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="商",nPriority=6,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="91" spans="3:43">
+        <v>{dwID=9464,nLevel=1,szNote="角",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="角",nPriority=7,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="91" spans="1:43">
       <c r="C91">
-        <v>9462</v>
+        <v>9465</v>
       </c>
       <c r="D91">
         <v>1</v>
       </c>
       <c r="K91" t="s">
-        <v>1688</v>
+        <v>1680</v>
       </c>
       <c r="L91" t="s">
         <v>613</v>
@@ -19247,13 +19286,13 @@
         <v>1</v>
       </c>
       <c r="AH91" t="s">
-        <v>1688</v>
+        <v>1680</v>
       </c>
       <c r="AI91">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ91" t="s">
-        <v>1676</v>
+        <v>1667</v>
       </c>
       <c r="AL91">
         <v>255</v>
@@ -19263,18 +19302,18 @@
       </c>
       <c r="AQ91" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=9462,nLevel=1,szNote="商",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="商",nPriority=6,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="92" spans="3:43">
+        <v>{dwID=9465,nLevel=1,szNote="角",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="角",nPriority=7,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="92" spans="1:43">
       <c r="C92">
-        <v>9463</v>
+        <v>9466</v>
       </c>
       <c r="D92">
         <v>1</v>
       </c>
       <c r="K92" t="s">
-        <v>1689</v>
+        <v>1680</v>
       </c>
       <c r="L92" t="s">
         <v>613</v>
@@ -19289,13 +19328,13 @@
         <v>1</v>
       </c>
       <c r="AH92" t="s">
-        <v>1689</v>
+        <v>1680</v>
       </c>
       <c r="AI92">
         <v>7</v>
       </c>
       <c r="AJ92" t="s">
-        <v>1676</v>
+        <v>1667</v>
       </c>
       <c r="AL92">
         <v>255</v>
@@ -19305,21 +19344,21 @@
       </c>
       <c r="AQ92" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=9463,nLevel=1,szNote="角",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="角",nPriority=7,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="93" spans="3:43">
+        <v>{dwID=9466,nLevel=1,szNote="角",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="角",nPriority=7,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="93" spans="1:43">
       <c r="C93">
-        <v>9464</v>
+        <v>631</v>
       </c>
       <c r="D93">
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>1689</v>
+        <v>1681</v>
       </c>
       <c r="L93" t="s">
-        <v>613</v>
+        <v>1675</v>
       </c>
       <c r="W93">
         <v>1</v>
@@ -19331,13 +19370,13 @@
         <v>1</v>
       </c>
       <c r="AH93" t="s">
-        <v>1689</v>
+        <v>1682</v>
       </c>
       <c r="AI93">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ93" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="AL93">
         <v>255</v>
@@ -19347,63 +19386,39 @@
       </c>
       <c r="AQ93" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=9464,nLevel=1,szNote="角",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="角",nPriority=7,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="94" spans="3:43">
-      <c r="C94">
-        <v>9465</v>
-      </c>
-      <c r="D94">
-        <v>1</v>
-      </c>
-      <c r="K94" t="s">
-        <v>1689</v>
-      </c>
-      <c r="L94" t="s">
-        <v>613</v>
-      </c>
-      <c r="W94">
-        <v>1</v>
-      </c>
-      <c r="X94">
-        <v>1</v>
-      </c>
-      <c r="AF94">
-        <v>1</v>
-      </c>
-      <c r="AH94" t="s">
-        <v>1689</v>
-      </c>
-      <c r="AI94">
-        <v>7</v>
-      </c>
-      <c r="AJ94" t="s">
-        <v>1676</v>
-      </c>
-      <c r="AL94">
-        <v>255</v>
-      </c>
-      <c r="AM94">
-        <v>1</v>
+        <v>{dwID=631,nLevel=1,szNote="握针",col={31,255,238,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="握",nPriority=5,col="#1FFFEEFF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="94" spans="1:43">
+      <c r="A94" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B94">
+        <v>-7</v>
       </c>
       <c r="AQ94" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=9465,nLevel=1,szNote="角",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="角",nPriority=7,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="95" spans="3:43">
+        <v>},[-7]={</v>
+      </c>
+    </row>
+    <row r="95" spans="1:43">
       <c r="C95">
-        <v>9466</v>
+        <v>631</v>
       </c>
       <c r="D95">
         <v>1</v>
       </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+      <c r="J95" t="s">
+        <v>1537</v>
+      </c>
       <c r="K95" t="s">
-        <v>1689</v>
+        <v>1681</v>
       </c>
       <c r="L95" t="s">
-        <v>613</v>
+        <v>1675</v>
       </c>
       <c r="W95">
         <v>1</v>
@@ -19415,13 +19430,13 @@
         <v>1</v>
       </c>
       <c r="AH95" t="s">
-        <v>1689</v>
+        <v>1682</v>
       </c>
       <c r="AI95">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ95" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="AL95">
         <v>255</v>
@@ -19431,114 +19446,12 @@
       </c>
       <c r="AQ95" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=9466,nLevel=1,szNote="角",col={0,255,0,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="角",nPriority=7,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="96" spans="3:43">
-      <c r="C96">
-        <v>631</v>
-      </c>
-      <c r="D96">
-        <v>1</v>
-      </c>
-      <c r="K96" t="s">
-        <v>1690</v>
-      </c>
-      <c r="L96" t="s">
-        <v>1684</v>
-      </c>
-      <c r="W96">
-        <v>1</v>
-      </c>
-      <c r="X96">
-        <v>1</v>
-      </c>
-      <c r="AF96">
-        <v>1</v>
-      </c>
-      <c r="AH96" t="s">
-        <v>1691</v>
-      </c>
-      <c r="AI96">
-        <v>5</v>
-      </c>
-      <c r="AJ96" t="s">
-        <v>1686</v>
-      </c>
-      <c r="AL96">
-        <v>255</v>
-      </c>
-      <c r="AM96">
-        <v>1</v>
-      </c>
+        <v>{dwID=631,nLevel=1,nScrutinyType=1,tKungFu={["SKILL#10028"]=true,},szNote="握针",col={31,255,238,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="握",nPriority=5,col="#1FFFEEFF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="96" spans="1:43">
       <c r="AQ96" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=631,nLevel=1,szNote="握针",col={31,255,238,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="握",nPriority=5,col="#1FFFEEFF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="97" spans="1:43">
-      <c r="A97" t="s">
-        <v>1692</v>
-      </c>
-      <c r="B97">
-        <v>-7</v>
-      </c>
-      <c r="AQ97" t="str">
-        <f t="shared" si="2"/>
-        <v>},[-7]={</v>
-      </c>
-    </row>
-    <row r="98" spans="1:43">
-      <c r="C98">
-        <v>631</v>
-      </c>
-      <c r="D98">
-        <v>1</v>
-      </c>
-      <c r="I98">
-        <v>1</v>
-      </c>
-      <c r="J98" t="s">
-        <v>1537</v>
-      </c>
-      <c r="K98" t="s">
-        <v>1690</v>
-      </c>
-      <c r="L98" t="s">
-        <v>1684</v>
-      </c>
-      <c r="W98">
-        <v>1</v>
-      </c>
-      <c r="X98">
-        <v>1</v>
-      </c>
-      <c r="AF98">
-        <v>1</v>
-      </c>
-      <c r="AH98" t="s">
-        <v>1691</v>
-      </c>
-      <c r="AI98">
-        <v>5</v>
-      </c>
-      <c r="AJ98" t="s">
-        <v>1686</v>
-      </c>
-      <c r="AL98">
-        <v>255</v>
-      </c>
-      <c r="AM98">
-        <v>1</v>
-      </c>
-      <c r="AQ98" t="str">
-        <f t="shared" si="2"/>
-        <v>{dwID=631,nLevel=1,nScrutinyType=1,tKungFu={["SKILL#10028"]=true,},szNote="握针",col={31,255,238,},[1]={bTeamPanel=true,bOnlySelfSrc=true,},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="握",nPriority=5,col="#1FFFEEFF",nColAlpha=255,bAttention=true,},},},</v>
-      </c>
-    </row>
-    <row r="99" spans="1:43">
-      <c r="AQ99" t="str">
-        <f>IF(B99&lt;&gt;"",IF(IFERROR(VALUE(C98),0)&lt;=0,"["&amp;B99&amp;"]={","},["&amp;B99&amp;"]={"),IF(C99&gt;0,"{dwID="&amp;C99&amp;","&amp;"nLevel="&amp;D99&amp;","&amp;IF(E99&gt;0,"nCount="&amp;E99&amp;",","")&amp;IF(F99&gt;0,"nIcon="&amp;F99&amp;",","")&amp;IF(G99&lt;&gt;"","szName="""&amp;G99&amp;""",","")&amp;IF(H99&gt;0,"bCheckLevel=true,","")&amp;IF(I99&gt;0,"nScrutinyType="&amp;I99&amp;",","")&amp;IF(J99&lt;&gt;"","tKungFu={"&amp;J99&amp;"},","")&amp;IF(K99&lt;&gt;"","szNote="""&amp;K99&amp;""",","")&amp;IF(L99&lt;&gt;"","col={"&amp;L99&amp;"},","")&amp;"[1]={"&amp;IF(M99&lt;&gt;"","tMark={"&amp;M99&amp;"},","")&amp;IF(N99&lt;&gt;"","szVoice="""&amp;N99&amp;""",","")&amp;IF(O99&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P99&gt;0,"bTeamChannel=true,","")&amp;IF(Q99&gt;0,"bWhisperChannel=true,","")&amp;IF(R99&gt;0,"bCenterAlarm=true,","")&amp;IF(S99&gt;0,"bScreenHead=true,","")&amp;IF(T99&gt;0,"bPartyBuffList=true,","")&amp;IF(U99&gt;0,"bBuffList=true,","")&amp;IF(V99&gt;0,"bFullScreen=true,","")&amp;IF(W99&gt;0,"bTeamPanel=true,","")&amp;IF(X99&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y99&lt;&gt;"","szVoice="""&amp;Y99&amp;""",","")&amp;IF(Z99&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA99&gt;0,"bTeamChannel=true,","")&amp;IF(AB99&gt;0,"bWhisperChannel=true,","")&amp;IF(AC99&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD99&gt;0,AH99&lt;&gt;"",AI99&gt;0,AJ99&lt;&gt;"",AK99&lt;&gt;"",AL99&gt;0,AM99&gt;0,AN99&gt;0,AO99&gt;0),"aCataclysmBuff={{"&amp;IF(AD99&gt;0,"nStackNum="&amp;AD99&amp;",","")&amp;IF(AE99&lt;&gt;"","szStackOp="""&amp;AE99&amp;""",","")&amp;IF(AF99&gt;0,"bOnlyMine=true,","")&amp;IF(AG99&gt;0,"bOnlyMe=true,","")&amp;IF(AH99&lt;&gt;"","szReminder="""&amp;AH99&amp;""",","")&amp;IF(AI99&gt;0,"nPriority="&amp;AI99&amp;",","")&amp;IF(AJ99&lt;&gt;"","col="""&amp;AJ99&amp;""",","")&amp;IF(AK99&lt;&gt;"","colScreenHead="""&amp;AK99&amp;""",","")&amp;IF(AL99&gt;0,"nColAlpha="&amp;AL99&amp;",","")&amp;IF(AM99&gt;0,"bAttention=true,","")&amp;IF(AN99&gt;0,"bCaution=true,","")&amp;IF(AO99&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP99&amp;"},","")&amp;IF(AR99&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR99:AAC99)&amp;"},","")&amp;"},",IF(C98&gt;0,"},","")&amp;IF(AND(B99="",C99="",OR(B98&lt;&gt;"",C98&lt;&gt;"")),"},}","")))</f>
         <v>},},}</v>
       </c>
     </row>
@@ -19552,7 +19465,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AS12"/>
+  <dimension ref="A1:AS15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:45">
@@ -19683,7 +19596,7 @@
         <v>1514</v>
       </c>
       <c r="AQ1" t="s">
-        <v>1693</v>
+        <v>1684</v>
       </c>
       <c r="AR1" t="s">
         <v>316</v>
@@ -19697,315 +19610,396 @@
         <v>-1</v>
       </c>
       <c r="AQ2" t="str">
-        <f t="shared" ref="AQ2:AQ12" si="0">IF(B2&lt;&gt;"",IF(IFERROR(VALUE(C1),0)&lt;=0,"["&amp;B2&amp;"]={","},["&amp;B2&amp;"]={"),IF(C2&gt;0,"{dwID="&amp;C2&amp;","&amp;"nLevel="&amp;D2&amp;","&amp;IF(E2&gt;0,"nCount="&amp;E2&amp;",","")&amp;IF(F2&gt;0,"nIcon="&amp;F2&amp;",","")&amp;IF(G2&lt;&gt;"","szName="""&amp;G2&amp;""",","")&amp;IF(H2&gt;0,"bCheckLevel=true,","")&amp;IF(I2&gt;0,"nScrutinyType="&amp;I2&amp;",","")&amp;IF(J2&lt;&gt;"","tKungFu={"&amp;J2&amp;"},","")&amp;IF(K2&lt;&gt;"","szNote="""&amp;K2&amp;""",","")&amp;IF(L2&lt;&gt;"","col={"&amp;L2&amp;"},","")&amp;"[1]={"&amp;IF(M2&lt;&gt;"","tMark={"&amp;M2&amp;"},","")&amp;IF(N2&lt;&gt;"","szVoice="""&amp;N2&amp;""",","")&amp;IF(O2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P2&gt;0,"bTeamChannel=true,","")&amp;IF(Q2&gt;0,"bWhisperChannel=true,","")&amp;IF(R2&gt;0,"bCenterAlarm=true,","")&amp;IF(S2&gt;0,"bScreenHead=true,","")&amp;IF(T2&gt;0,"bPartyBuffList=true,","")&amp;IF(U2&gt;0,"bBuffList=true,","")&amp;IF(V2&gt;0,"bFullScreen=true,","")&amp;IF(W2&gt;0,"bTeamPanel=true,","")&amp;IF(X2&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y2&lt;&gt;"","szVoice="""&amp;Y2&amp;""",","")&amp;IF(Z2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA2&gt;0,"bTeamChannel=true,","")&amp;IF(AB2&gt;0,"bWhisperChannel=true,","")&amp;IF(AC2&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD2&gt;0,AH2&lt;&gt;"",AI2&gt;0,AJ2&lt;&gt;"",AK2&lt;&gt;"",AL2&gt;0,AM2&gt;0,AN2&gt;0,AO2&gt;0),"aCataclysmBuff={{"&amp;IF(AD2&gt;0,"nStackNum="&amp;AD2&amp;",","")&amp;IF(AE2&lt;&gt;"","szStackOp="""&amp;AE2&amp;""",","")&amp;IF(AF2&gt;0,"bOnlyMine=true,","")&amp;IF(AG2&gt;0,"bOnlyMe=true,","")&amp;IF(AH2&lt;&gt;"","szReminder="""&amp;AH2&amp;""",","")&amp;IF(AI2&gt;0,"nPriority="&amp;AI2&amp;",","")&amp;IF(AJ2&lt;&gt;"","col="""&amp;AJ2&amp;""",","")&amp;IF(AK2&lt;&gt;"","colScreenHead="""&amp;AK2&amp;""",","")&amp;IF(AL2&gt;0,"nColAlpha="&amp;AL2&amp;",","")&amp;IF(AM2&gt;0,"bAttention=true,","")&amp;IF(AN2&gt;0,"bCaution=true,","")&amp;IF(AO2&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP2&amp;"},","")&amp;IF(AR2&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR2:AAC2)&amp;"},","")&amp;"},",IF(C1&gt;0,"},","")&amp;IF(AND(B2="",C2="",OR(B1&lt;&gt;"",C1&lt;&gt;"")),"},}","")))</f>
+        <f>IF(B2&lt;&gt;"",IF(IFERROR(VALUE(C1),0)&lt;=0,"["&amp;B2&amp;"]={","},["&amp;B2&amp;"]={"),IF(C2&gt;0,"{dwID="&amp;C2&amp;","&amp;"nLevel="&amp;D2&amp;","&amp;IF(E2&gt;0,"nCount="&amp;E2&amp;",","")&amp;IF(F2&gt;0,"nIcon="&amp;F2&amp;",","")&amp;IF(G2&lt;&gt;"","szName="""&amp;G2&amp;""",","")&amp;IF(H2&gt;0,"bCheckLevel=true,","")&amp;IF(I2&gt;0,"nScrutinyType="&amp;I2&amp;",","")&amp;IF(J2&lt;&gt;"","tKungFu={"&amp;J2&amp;"},","")&amp;IF(K2&lt;&gt;"","szNote="""&amp;K2&amp;""",","")&amp;IF(L2&lt;&gt;"","col={"&amp;L2&amp;"},","")&amp;"[1]={"&amp;IF(M2&lt;&gt;"","tMark={"&amp;M2&amp;"},","")&amp;IF(N2&lt;&gt;"","szVoice="""&amp;N2&amp;""",","")&amp;IF(O2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P2&gt;0,"bTeamChannel=true,","")&amp;IF(Q2&gt;0,"bWhisperChannel=true,","")&amp;IF(R2&gt;0,"bCenterAlarm=true,","")&amp;IF(S2&gt;0,"bScreenHead=true,","")&amp;IF(T2&gt;0,"bPartyBuffList=true,","")&amp;IF(U2&gt;0,"bBuffList=true,","")&amp;IF(V2&gt;0,"bFullScreen=true,","")&amp;IF(W2&gt;0,"bTeamPanel=true,","")&amp;IF(X2&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y2&lt;&gt;"","szVoice="""&amp;Y2&amp;""",","")&amp;IF(Z2&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA2&gt;0,"bTeamChannel=true,","")&amp;IF(AB2&gt;0,"bWhisperChannel=true,","")&amp;IF(AC2&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD2&gt;0,AH2&lt;&gt;"",AI2&gt;0,AJ2&lt;&gt;"",AK2&lt;&gt;"",AL2&gt;0,AM2&gt;0,AN2&gt;0,AO2&gt;0),"aCataclysmBuff={{"&amp;IF(AD2&gt;0,"nStackNum="&amp;AD2&amp;",","")&amp;IF(AE2&lt;&gt;"","szStackOp="""&amp;AE2&amp;""",","")&amp;IF(AF2&gt;0,"bOnlyMine=true,","")&amp;IF(AG2&gt;0,"bOnlyMe=true,","")&amp;IF(AH2&lt;&gt;"","szReminder="""&amp;AH2&amp;""",","")&amp;IF(AI2&gt;0,"nPriority="&amp;AI2&amp;",","")&amp;IF(AJ2&lt;&gt;"","col="""&amp;AJ2&amp;""",","")&amp;IF(AK2&lt;&gt;"","colScreenHead="""&amp;AK2&amp;""",","")&amp;IF(AL2&gt;0,"nColAlpha="&amp;AL2&amp;",","")&amp;IF(AM2&gt;0,"bAttention=true,","")&amp;IF(AN2&gt;0,"bCaution=true,","")&amp;IF(AO2&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP2&amp;"},","")&amp;IF(AR2&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR2:AAC2)&amp;"},","")&amp;"},",IF(C1&gt;0,"},","")&amp;IF(AND(B2="",C2="",OR(B1&lt;&gt;"",C1&lt;&gt;"")),"},}","")))</f>
         <v>[-1]={</v>
       </c>
     </row>
-    <row r="3" spans="1:45">
-      <c r="C3">
+    <row r="3" s="1" customFormat="1" spans="1:45">
+      <c r="C3" s="1">
+        <v>27689</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="AQ3" t="str">
+        <f t="shared" ref="AQ3:AQ15" si="0">IF(B3&lt;&gt;"",IF(IFERROR(VALUE(C2),0)&lt;=0,"["&amp;B3&amp;"]={","},["&amp;B3&amp;"]={"),IF(C3&gt;0,"{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"nIcon="&amp;F3&amp;",","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&gt;0,"bCheckLevel=true,","")&amp;IF(I3&gt;0,"nScrutinyType="&amp;I3&amp;",","")&amp;IF(J3&lt;&gt;"","tKungFu={"&amp;J3&amp;"},","")&amp;IF(K3&lt;&gt;"","szNote="""&amp;K3&amp;""",","")&amp;IF(L3&lt;&gt;"","col={"&amp;L3&amp;"},","")&amp;"[1]={"&amp;IF(M3&lt;&gt;"","tMark={"&amp;M3&amp;"},","")&amp;IF(N3&lt;&gt;"","szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P3&gt;0,"bTeamChannel=true,","")&amp;IF(Q3&gt;0,"bWhisperChannel=true,","")&amp;IF(R3&gt;0,"bCenterAlarm=true,","")&amp;IF(S3&gt;0,"bScreenHead=true,","")&amp;IF(T3&gt;0,"bPartyBuffList=true,","")&amp;IF(U3&gt;0,"bBuffList=true,","")&amp;IF(V3&gt;0,"bFullScreen=true,","")&amp;IF(W3&gt;0,"bTeamPanel=true,","")&amp;IF(X3&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y3&lt;&gt;"","szVoice="""&amp;Y3&amp;""",","")&amp;IF(Z3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA3&gt;0,"bTeamChannel=true,","")&amp;IF(AB3&gt;0,"bWhisperChannel=true,","")&amp;IF(AC3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD3&gt;0,AH3&lt;&gt;"",AI3&gt;0,AJ3&lt;&gt;"",AK3&lt;&gt;"",AL3&gt;0,AM3&gt;0,AN3&gt;0,AO3&gt;0),"aCataclysmBuff={{"&amp;IF(AD3&gt;0,"nStackNum="&amp;AD3&amp;",","")&amp;IF(AE3&lt;&gt;"","szStackOp="""&amp;AE3&amp;""",","")&amp;IF(AF3&gt;0,"bOnlyMine=true,","")&amp;IF(AG3&gt;0,"bOnlyMe=true,","")&amp;IF(AH3&lt;&gt;"","szReminder="""&amp;AH3&amp;""",","")&amp;IF(AI3&gt;0,"nPriority="&amp;AI3&amp;",","")&amp;IF(AJ3&lt;&gt;"","col="""&amp;AJ3&amp;""",","")&amp;IF(AK3&lt;&gt;"","colScreenHead="""&amp;AK3&amp;""",","")&amp;IF(AL3&gt;0,"nColAlpha="&amp;AL3&amp;",","")&amp;IF(AM3&gt;0,"bAttention=true,","")&amp;IF(AN3&gt;0,"bCaution=true,","")&amp;IF(AO3&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP3&amp;"},","")&amp;IF(AR3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR3:AAC3)&amp;"},","")&amp;"},",IF(C2&gt;0,"},","")&amp;IF(AND(B3="",C3="",OR(B2&lt;&gt;"",C2&lt;&gt;"")),"},}","")))</f>
+        <v>{dwID=27689,nLevel=1,nScrutinyType=1,szNote="缘会·今夕何夕",col={0,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=21596,nFrame=5,nTime=0,szName="缘会·今夕何夕",key="缘会·今夕何夕",},{nClass=2,nIcon=21596,nFrame=2,nTime=60,szName="香膏·绝世奇遇·已消失",key="缘会·今夕何夕",},},},</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>1686</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:45">
+      <c r="C4" s="1">
+        <v>27663</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>1688</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="AQ4" t="str">
+        <f t="shared" si="0"/>
+        <v>{dwID=27663,nLevel=1,nScrutinyType=1,szNote="缘会·月出皎兮",col={0,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=21600,nFrame=5,nTime=0,szName="缘会·月出皎兮",key="缘会·月出皎兮",},{nClass=2,nIcon=21600,nFrame=2,nTime=60,szName="香膏·普通奇遇·已消失",key="缘会·月出皎兮",},},},</v>
+      </c>
+      <c r="AR4" s="1" t="s">
+        <v>1689</v>
+      </c>
+      <c r="AS4" s="1" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:45">
+      <c r="C5" s="1">
+        <v>27662</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>1691</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="AQ5" t="str">
+        <f t="shared" si="0"/>
+        <v>{dwID=27662,nLevel=1,nScrutinyType=1,szNote="缘会·山有扶苏",col={0,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=21600,nFrame=5,nTime=0,szName="缘会·山有扶苏",key="缘会·山有扶苏",},{nClass=2,nIcon=21600,nFrame=2,nTime=60,szName="香膏·宠物奇遇·已消失",key="缘会·山有扶苏",},},},</v>
+      </c>
+      <c r="AR5" s="1" t="s">
+        <v>1692</v>
+      </c>
+      <c r="AS5" s="1" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="6" spans="1:45">
+      <c r="C6">
         <v>30710</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
         <v>1694</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
         <v>1695</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L6" t="s">
         <v>622</v>
       </c>
-      <c r="U3">
-        <v>1</v>
-      </c>
-      <c r="AQ3" t="str">
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=30710,nLevel=1,szName="头计数",nScrutinyType=1,szNote="3次后额外伤害或治疗",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
-    <row r="4" spans="1:45">
-      <c r="C4">
+    <row r="7" spans="1:45">
+      <c r="C7">
         <v>15455</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="F4">
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="F7">
         <v>7293</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G7" t="s">
         <v>1696</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
         <v>1697</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L7" t="s">
         <v>622</v>
       </c>
-      <c r="U4">
-        <v>1</v>
-      </c>
-      <c r="AQ4" t="str">
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=15455,nLevel=1,nIcon=7293,szName="1%腰",bCheckLevel=true,nScrutinyType=1,szNote="输出伤害波动-伤腰大附魔增伤1%",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
-    <row r="5" spans="1:45">
-      <c r="C5">
+    <row r="8" spans="1:45">
+      <c r="C8">
         <v>15455</v>
       </c>
-      <c r="D5">
+      <c r="D8">
         <v>2</v>
       </c>
-      <c r="F5">
+      <c r="F8">
         <v>7371</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G8" t="s">
         <v>1698</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
         <v>1699</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L8" t="s">
         <v>622</v>
       </c>
-      <c r="U5">
-        <v>1</v>
-      </c>
-      <c r="AQ5" t="str">
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=15455,nLevel=2,nIcon=7371,szName="5%腰",bCheckLevel=true,nScrutinyType=1,szNote="输出伤害波动-伤腰大附魔增伤5%",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
-    <row r="6" spans="1:45">
-      <c r="C6">
+    <row r="9" spans="1:45">
+      <c r="C9">
         <v>21953</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1650</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K9" t="s">
         <v>1700</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L9" t="s">
         <v>596</v>
       </c>
-      <c r="S6">
-        <v>1</v>
-      </c>
-      <c r="T6">
-        <v>1</v>
-      </c>
-      <c r="U6">
-        <v>1</v>
-      </c>
-      <c r="W6">
-        <v>1</v>
-      </c>
-      <c r="AH6" t="s">
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="s">
         <v>1701</v>
       </c>
-      <c r="AI6">
+      <c r="AI9">
         <v>6</v>
       </c>
-      <c r="AJ6" t="s">
+      <c r="AJ9" t="s">
         <v>1702</v>
       </c>
-      <c r="AL6">
+      <c r="AL9">
         <v>255</v>
       </c>
-      <c r="AQ6" t="str">
+      <c r="AQ9" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=21953,nLevel=1,tKungFu={["SKILL#10028"]=true,["SKILL#10080"]=true,["SKILL#10176"]=true,["SKILL#10448"]=true,["SKILL#10626"]=true,},szNote="枯木",col={255,150,0,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="枯",nPriority=6,col="#FA9B00FF",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=15422,nFrame=6,nTime="1,奶【{$receiver}】;2,奶【{$receiver}】;3,奶【{$receiver}】;30,奶【{$receiver}】",szName="1,奶【{$receiver}】;2,奶【{$receiver}】;3,奶【{$receiver}】;30,奶【{$receiver}】;",key="枯木{$receiver}",},{nClass=2,nIcon=15422,nFrame=6,nTime=0,szName="",key="枯木{$receiver}",},},},</v>
       </c>
-      <c r="AR6" t="s">
+      <c r="AR9" t="s">
         <v>1703</v>
       </c>
-      <c r="AS6" t="s">
+      <c r="AS9" t="s">
         <v>1704</v>
       </c>
     </row>
-    <row r="7" spans="1:45">
-      <c r="C7">
+    <row r="10" spans="1:45">
+      <c r="C10">
         <v>20554</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>1650</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K10" t="s">
         <v>1700</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L10" t="s">
         <v>596</v>
       </c>
-      <c r="S7">
-        <v>1</v>
-      </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
-      <c r="U7">
-        <v>1</v>
-      </c>
-      <c r="W7">
-        <v>1</v>
-      </c>
-      <c r="AH7" t="s">
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="s">
         <v>1701</v>
       </c>
-      <c r="AI7">
+      <c r="AI10">
         <v>6</v>
       </c>
-      <c r="AJ7" t="s">
+      <c r="AJ10" t="s">
         <v>1705</v>
       </c>
-      <c r="AL7">
+      <c r="AL10">
         <v>255</v>
       </c>
-      <c r="AQ7" t="str">
+      <c r="AQ10" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=20554,nLevel=1,tKungFu={["SKILL#10028"]=true,["SKILL#10080"]=true,["SKILL#10176"]=true,["SKILL#10448"]=true,["SKILL#10626"]=true,},szNote="枯木",col={255,150,0,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="枯",nPriority=6,col="#FF9600FF",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=15422,nFrame=6,nTime="1,奶【{$receiver}】;2,奶【{$receiver}】;3,奶【{$receiver}】;30,奶【{$receiver}】",szName="1,奶[{$receiver}];2,奶[{$receiver}];3,奶[{$receiver}];30,奶[{$receiver}];",key="枯木{$receiver}",},{nClass=2,nIcon=15422,nFrame=5,nTime=0,szName="",key="枯木{$receiver}",},},},</v>
       </c>
-      <c r="AR7" t="s">
+      <c r="AR10" t="s">
         <v>1706</v>
       </c>
-      <c r="AS7" t="s">
+      <c r="AS10" t="s">
         <v>1707</v>
       </c>
     </row>
-    <row r="8" spans="1:45">
-      <c r="A8" t="s">
-        <v>1657</v>
-      </c>
-      <c r="B8">
+    <row r="11" spans="1:45">
+      <c r="A11" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B11">
         <v>-3</v>
       </c>
-      <c r="AQ8" t="str">
+      <c r="AQ11" t="str">
         <f t="shared" si="0"/>
         <v>},[-3]={</v>
       </c>
     </row>
-    <row r="9" spans="1:45">
-      <c r="C9">
+    <row r="12" spans="1:45">
+      <c r="C12">
         <v>2316</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="AF9">
-        <v>1</v>
-      </c>
-      <c r="AH9" t="s">
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="AF12">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="s">
         <v>1708</v>
       </c>
-      <c r="AI9">
+      <c r="AI12">
         <v>5</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>1676</v>
-      </c>
-      <c r="AL9">
+      <c r="AJ12" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AL12">
         <v>255</v>
       </c>
-      <c r="AM9">
-        <v>1</v>
-      </c>
-      <c r="AQ9" t="str">
+      <c r="AM12">
+        <v>1</v>
+      </c>
+      <c r="AQ12" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=2316,nLevel=1,[1]={},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="蛊",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
       </c>
     </row>
-    <row r="10" spans="1:45">
-      <c r="C10">
+    <row r="13" spans="1:45">
+      <c r="C13">
         <v>26986</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="AF10">
-        <v>1</v>
-      </c>
-      <c r="AH10" t="s">
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="AF13">
+        <v>1</v>
+      </c>
+      <c r="AH13" t="s">
         <v>1709</v>
       </c>
-      <c r="AI10">
+      <c r="AI13">
         <v>5</v>
       </c>
-      <c r="AJ10" t="s">
-        <v>1676</v>
-      </c>
-      <c r="AL10">
+      <c r="AJ13" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AL13">
         <v>255</v>
       </c>
-      <c r="AM10">
-        <v>1</v>
-      </c>
-      <c r="AQ10" t="str">
+      <c r="AM13">
+        <v>1</v>
+      </c>
+      <c r="AQ13" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=26986,nLevel=1,[1]={},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="音",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
       </c>
     </row>
-    <row r="11" spans="1:45">
-      <c r="C11">
+    <row r="14" spans="1:45">
+      <c r="C14">
         <v>9335</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="F11">
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="F14">
         <v>11863</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K14" t="s">
         <v>1710</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L14" t="s">
         <v>1711</v>
       </c>
-      <c r="AF11">
-        <v>1</v>
-      </c>
-      <c r="AH11" t="s">
+      <c r="AF14">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="s">
         <v>1712</v>
       </c>
-      <c r="AI11">
+      <c r="AI14">
         <v>3</v>
       </c>
-      <c r="AJ11" t="s">
+      <c r="AJ14" t="s">
         <v>1713</v>
       </c>
-      <c r="AL11">
+      <c r="AL14">
         <v>255</v>
       </c>
-      <c r="AQ11" t="str">
+      <c r="AQ14" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=9335,nLevel=1,nIcon=11863,szNote="无法获得梅花三弄",col={255,238,255,},[1]={},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="落",nPriority=3,col="#FFEEEEFF",nColAlpha=255,},},},</v>
       </c>
     </row>
-    <row r="12" spans="1:45">
-      <c r="AQ12" t="str">
+    <row r="15" spans="1:45">
+      <c r="AQ15" t="str">
         <f t="shared" si="0"/>
         <v>},},}</v>
       </c>
